--- a/data/european_offshore_wind_capex.xlsx
+++ b/data/european_offshore_wind_capex.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\weron\Pulpit\sem3\ds_workshop\WindFarm\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E1E4A1-7783-4DC4-A1E7-7583DA59EF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F86846-A451-40C2-85C3-D990FB56EBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="18672" xr2:uid="{D4FCA4BE-944B-479A-AF27-5DDC1E18E177}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{D4FCA4BE-944B-479A-AF27-5DDC1E18E177}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3104,9 +3104,6 @@
     <t>25,9</t>
   </si>
   <si>
-    <t>area</t>
-  </si>
-  <si>
     <t>41.3</t>
   </si>
   <si>
@@ -3174,6 +3171,9 @@
   </si>
   <si>
     <t>247</t>
+  </si>
+  <si>
+    <t>area_sqkm</t>
   </si>
 </sst>
 </file>
@@ -3641,7 +3641,7 @@
         <v>845</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1014</v>
+        <v>1037</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -6455,7 +6455,7 @@
         <v>881</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>22</v>
@@ -6819,7 +6819,7 @@
         <v>886</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>22</v>
@@ -6967,7 +6967,7 @@
         <v>888</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>22</v>
@@ -7041,7 +7041,7 @@
         <v>924</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>22</v>
@@ -7411,7 +7411,7 @@
         <v>891</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>280</v>
@@ -7559,7 +7559,7 @@
         <v>927</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>280</v>
@@ -7855,7 +7855,7 @@
         <v>892</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>280</v>
@@ -8077,7 +8077,7 @@
         <v>932</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>280</v>
@@ -8447,7 +8447,7 @@
         <v>895</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>280</v>
@@ -8595,7 +8595,7 @@
         <v>897</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>280</v>
@@ -8669,7 +8669,7 @@
         <v>898</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>280</v>
@@ -8817,7 +8817,7 @@
         <v>899</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>280</v>
@@ -9187,7 +9187,7 @@
         <v>902</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>280</v>
@@ -9261,7 +9261,7 @@
         <v>903</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>280</v>
@@ -9335,7 +9335,7 @@
         <v>904</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>280</v>
@@ -9409,7 +9409,7 @@
         <v>905</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>280</v>
@@ -9853,7 +9853,7 @@
         <v>940</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>408</v>
@@ -9927,7 +9927,7 @@
         <v>907</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>408</v>
@@ -10001,7 +10001,7 @@
         <v>908</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>408</v>
@@ -10149,7 +10149,7 @@
         <v>910</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>408</v>
@@ -10223,7 +10223,7 @@
         <v>911</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>408</v>
@@ -10371,7 +10371,7 @@
         <v>912</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>408</v>
@@ -10741,7 +10741,7 @@
         <v>927</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>408</v>
@@ -10815,7 +10815,7 @@
         <v>942</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>408</v>
@@ -11037,7 +11037,7 @@
         <v>927</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>408</v>
@@ -11185,7 +11185,7 @@
         <v>944</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>408</v>
@@ -11333,7 +11333,7 @@
         <v>920</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E106" s="5" t="s">
         <v>497</v>
@@ -11407,7 +11407,7 @@
         <v>921</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E107" s="5" t="s">
         <v>497</v>

--- a/data/european_offshore_wind_capex.xlsx
+++ b/data/european_offshore_wind_capex.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\weron\Pulpit\sem3\ds_workshop\WindFarm\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F86846-A451-40C2-85C3-D990FB56EBF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07962A8-B80E-4C3F-B87F-08A04A07C6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{D4FCA4BE-944B-479A-AF27-5DDC1E18E177}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4207" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4207" uniqueCount="1046">
   <si>
     <t>wind_farm_name</t>
   </si>
@@ -3174,6 +3174,30 @@
   </si>
   <si>
     <t>area_sqkm</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>85-96</t>
+  </si>
+  <si>
+    <t>140-214</t>
+  </si>
+  <si>
+    <t>77-102</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>10-25</t>
+  </si>
+  <si>
+    <t>600-900</t>
+  </si>
+  <si>
+    <t>10-15</t>
   </si>
 </sst>
 </file>
@@ -4382,7 +4406,7 @@
         <v>36</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>30</v>
@@ -5606,7 +5630,7 @@
         <v>30</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>30</v>
+        <v>1038</v>
       </c>
       <c r="L28" s="4" t="s">
         <v>30</v>
@@ -5678,7 +5702,7 @@
         <v>169</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>30</v>
+        <v>216</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>170</v>
@@ -9726,7 +9750,7 @@
         <v>30</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>30</v>
+        <v>1039</v>
       </c>
       <c r="L84" s="5" t="s">
         <v>403</v>
@@ -10392,7 +10416,7 @@
         <v>449</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>30</v>
+        <v>175</v>
       </c>
       <c r="L93" s="4" t="s">
         <v>30</v>
@@ -11132,7 +11156,7 @@
         <v>30</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="L103" s="4" t="s">
         <v>30</v>
@@ -11794,7 +11818,7 @@
         <v>30</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>30</v>
+        <v>267</v>
       </c>
       <c r="L112" s="4" t="s">
         <v>30</v>
@@ -11866,7 +11890,7 @@
         <v>30</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>30</v>
+        <v>1040</v>
       </c>
       <c r="L113" s="4" t="s">
         <v>30</v>
@@ -12010,7 +12034,7 @@
         <v>30</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>30</v>
+        <v>216</v>
       </c>
       <c r="L115" s="5" t="s">
         <v>535</v>
@@ -13378,7 +13402,7 @@
         <v>30</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>30</v>
+        <v>1041</v>
       </c>
       <c r="L134" s="4" t="s">
         <v>30</v>
@@ -13450,7 +13474,7 @@
         <v>30</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>30</v>
+        <v>1042</v>
       </c>
       <c r="L135" s="4" t="s">
         <v>30</v>
@@ -14170,7 +14194,7 @@
         <v>30</v>
       </c>
       <c r="K145" s="4" t="s">
-        <v>30</v>
+        <v>325</v>
       </c>
       <c r="L145" s="4" t="s">
         <v>30</v>
@@ -14242,7 +14266,7 @@
         <v>30</v>
       </c>
       <c r="K146" s="4" t="s">
-        <v>30</v>
+        <v>325</v>
       </c>
       <c r="L146" s="4" t="s">
         <v>30</v>
@@ -15598,7 +15622,7 @@
         <v>66</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>30</v>
+        <v>1044</v>
       </c>
       <c r="H165" s="5" t="s">
         <v>30</v>
@@ -15610,7 +15634,7 @@
         <v>30</v>
       </c>
       <c r="K165" s="4" t="s">
-        <v>30</v>
+        <v>1043</v>
       </c>
       <c r="L165" s="4" t="s">
         <v>30</v>
@@ -15898,7 +15922,7 @@
         <v>30</v>
       </c>
       <c r="K169" s="4" t="s">
-        <v>30</v>
+        <v>615</v>
       </c>
       <c r="L169" s="5" t="s">
         <v>693</v>
@@ -15958,7 +15982,7 @@
         <v>30</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>30</v>
+        <v>397</v>
       </c>
       <c r="H170" s="5" t="s">
         <v>30</v>
@@ -15970,7 +15994,7 @@
         <v>30</v>
       </c>
       <c r="K170" s="4" t="s">
-        <v>30</v>
+        <v>734</v>
       </c>
       <c r="L170" s="4" t="s">
         <v>30</v>
@@ -16186,7 +16210,7 @@
         <v>30</v>
       </c>
       <c r="K173" s="4" t="s">
-        <v>30</v>
+        <v>551</v>
       </c>
       <c r="L173" s="4" t="s">
         <v>30</v>
@@ -16546,7 +16570,7 @@
         <v>30</v>
       </c>
       <c r="K178" s="4" t="s">
-        <v>30</v>
+        <v>233</v>
       </c>
       <c r="L178" s="4" t="s">
         <v>30</v>
@@ -16906,7 +16930,7 @@
         <v>30</v>
       </c>
       <c r="K183" s="4" t="s">
-        <v>30</v>
+        <v>1045</v>
       </c>
       <c r="L183" s="4" t="s">
         <v>30</v>

--- a/data/european_offshore_wind_capex.xlsx
+++ b/data/european_offshore_wind_capex.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\weron\Pulpit\sem3\ds_workshop\poc2\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdudz\Documents\WindFarm\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566A5A43-8B28-4265-85BF-1C7D71D25348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF32D48D-F567-4910-9DA2-3034E6CBBC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{D4FCA4BE-944B-479A-AF27-5DDC1E18E177}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4FCA4BE-944B-479A-AF27-5DDC1E18E177}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Z$183</definedName>
     <definedName name="european_offshore_wind_capex__2" localSheetId="0">Sheet1!$A$1:$Z$183</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4218" uniqueCount="1087">
   <si>
     <t>wind_farm_name</t>
   </si>
@@ -3252,6 +3253,75 @@
   </si>
   <si>
     <t>Siemens</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>USD 212.273 millon</t>
+  </si>
+  <si>
+    <t>EUR 7.4 billion</t>
+  </si>
+  <si>
+    <t>EUR 4-5 million</t>
+  </si>
+  <si>
+    <t>EUR 17.85 million</t>
+  </si>
+  <si>
+    <t>EUR 2.95 billion</t>
+  </si>
+  <si>
+    <t>EUR 3.4 billion</t>
+  </si>
+  <si>
+    <t>EUR 120-140 million</t>
+  </si>
+  <si>
+    <t>EUR 1.5 billion</t>
+  </si>
+  <si>
+    <t>EUR 50 million</t>
+  </si>
+  <si>
+    <t>EUR 3.2 billion</t>
+  </si>
+  <si>
+    <t>EUR 1.5-1.8 billion</t>
+  </si>
+  <si>
+    <t>EUR 2.5-3 billion</t>
+  </si>
+  <si>
+    <t>EUR 3.978 bullion</t>
+  </si>
+  <si>
+    <t>EUR 3.920 billion</t>
+  </si>
+  <si>
+    <t>EUR 4-4.5 billion</t>
+  </si>
+  <si>
+    <t>EUR 4.5-5 billion</t>
+  </si>
+  <si>
+    <t>EUR 1.5-2.2 billion</t>
+  </si>
+  <si>
+    <t>EUR 3.75-4 billion</t>
+  </si>
+  <si>
+    <t>EUR 50-60 million</t>
+  </si>
+  <si>
+    <t>USD 990.801 million</t>
+  </si>
+  <si>
+    <t>EUR 30-40 million</t>
+  </si>
+  <si>
+    <t>USD 1.71 billion</t>
   </si>
 </sst>
 </file>
@@ -3383,9 +3453,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3423,7 +3493,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3529,7 +3599,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3671,7 +3741,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3680,35 +3750,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B77FC0E0-AD80-4AE8-A6B7-6191F2A456DA}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" customWidth="1"/>
-    <col min="3" max="3" width="32.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.77734375" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" customWidth="1"/>
-    <col min="6" max="6" width="17.77734375" customWidth="1"/>
-    <col min="7" max="9" width="20.21875" customWidth="1"/>
-    <col min="10" max="10" width="45.21875" customWidth="1"/>
-    <col min="11" max="11" width="28.44140625" customWidth="1"/>
-    <col min="12" max="12" width="14.109375" customWidth="1"/>
-    <col min="13" max="13" width="22.109375" customWidth="1"/>
-    <col min="14" max="14" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="9" width="20.28515625" customWidth="1"/>
+    <col min="10" max="10" width="45.28515625" customWidth="1"/>
+    <col min="11" max="11" width="28.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="22.140625" customWidth="1"/>
+    <col min="14" max="14" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="23" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3788,7 +3858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -3864,7 +3934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -3940,7 +4010,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
@@ -4016,7 +4086,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
@@ -4090,7 +4160,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>54</v>
       </c>
@@ -4164,7 +4234,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>56</v>
       </c>
@@ -4238,7 +4308,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
@@ -4314,7 +4384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
@@ -4390,7 +4460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>69</v>
       </c>
@@ -4466,7 +4536,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>73</v>
       </c>
@@ -4476,7 +4546,9 @@
       <c r="C11" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="5" t="s">
+        <v>1064</v>
+      </c>
       <c r="E11" s="5" t="s">
         <v>22</v>
       </c>
@@ -4542,7 +4614,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>75</v>
       </c>
@@ -4618,7 +4690,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>82</v>
       </c>
@@ -4692,7 +4764,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>88</v>
       </c>
@@ -4766,7 +4838,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>94</v>
       </c>
@@ -4840,7 +4912,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>101</v>
       </c>
@@ -4914,7 +4986,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>106</v>
       </c>
@@ -4988,7 +5060,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>113</v>
       </c>
@@ -5062,7 +5134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>118</v>
       </c>
@@ -5136,7 +5208,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>125</v>
       </c>
@@ -5210,7 +5282,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>130</v>
       </c>
@@ -5284,7 +5356,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>134</v>
       </c>
@@ -5358,7 +5430,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>140</v>
       </c>
@@ -5432,7 +5504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>145</v>
       </c>
@@ -5506,7 +5578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>149</v>
       </c>
@@ -5580,7 +5652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>154</v>
       </c>
@@ -5654,7 +5726,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>159</v>
       </c>
@@ -5728,7 +5800,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>163</v>
       </c>
@@ -5802,7 +5874,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>166</v>
       </c>
@@ -5876,7 +5948,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>171</v>
       </c>
@@ -5950,7 +6022,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>177</v>
       </c>
@@ -6024,7 +6096,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>181</v>
       </c>
@@ -6098,7 +6170,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>187</v>
       </c>
@@ -6172,7 +6244,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>192</v>
       </c>
@@ -6246,7 +6318,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>196</v>
       </c>
@@ -6320,7 +6392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>203</v>
       </c>
@@ -6394,7 +6466,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>207</v>
       </c>
@@ -6468,7 +6540,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>213</v>
       </c>
@@ -6544,7 +6616,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>218</v>
       </c>
@@ -6620,7 +6692,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>221</v>
       </c>
@@ -6696,7 +6768,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>225</v>
       </c>
@@ -6770,7 +6842,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>229</v>
       </c>
@@ -6844,7 +6916,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>234</v>
       </c>
@@ -6879,7 +6951,7 @@
         <v>239</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>30</v>
+        <v>1065</v>
       </c>
       <c r="O43" s="5" t="s">
         <v>30</v>
@@ -6918,7 +6990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>240</v>
       </c>
@@ -6994,7 +7066,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:26" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:26" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>246</v>
       </c>
@@ -7070,7 +7142,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:26" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:26" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>251</v>
       </c>
@@ -7146,7 +7218,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>258</v>
       </c>
@@ -7222,7 +7294,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>261</v>
       </c>
@@ -7298,7 +7370,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>266</v>
       </c>
@@ -7374,7 +7446,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>273</v>
       </c>
@@ -7450,7 +7522,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>279</v>
       </c>
@@ -7526,7 +7598,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>286</v>
       </c>
@@ -7602,7 +7674,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>292</v>
       </c>
@@ -7678,7 +7750,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>297</v>
       </c>
@@ -7754,7 +7826,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>301</v>
       </c>
@@ -7830,7 +7902,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>304</v>
       </c>
@@ -7906,7 +7978,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>308</v>
       </c>
@@ -7982,7 +8054,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>311</v>
       </c>
@@ -8058,7 +8130,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>314</v>
       </c>
@@ -8134,7 +8206,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>320</v>
       </c>
@@ -8210,7 +8282,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>327</v>
       </c>
@@ -8286,7 +8358,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>329</v>
       </c>
@@ -8362,7 +8434,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>333</v>
       </c>
@@ -8438,7 +8510,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>337</v>
       </c>
@@ -8514,7 +8586,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>339</v>
       </c>
@@ -8590,7 +8662,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>342</v>
       </c>
@@ -8666,7 +8738,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>345</v>
       </c>
@@ -8742,7 +8814,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>347</v>
       </c>
@@ -8818,7 +8890,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>351</v>
       </c>
@@ -8894,7 +8966,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>354</v>
       </c>
@@ -8970,7 +9042,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>360</v>
       </c>
@@ -9046,7 +9118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>363</v>
       </c>
@@ -9122,7 +9194,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>366</v>
       </c>
@@ -9198,7 +9270,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>369</v>
       </c>
@@ -9274,7 +9346,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
         <v>371</v>
       </c>
@@ -9350,7 +9422,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>375</v>
       </c>
@@ -9426,7 +9498,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>379</v>
       </c>
@@ -9502,7 +9574,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>383</v>
       </c>
@@ -9578,7 +9650,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>388</v>
       </c>
@@ -9654,7 +9726,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>391</v>
       </c>
@@ -9730,7 +9802,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
         <v>393</v>
       </c>
@@ -9806,7 +9878,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>395</v>
       </c>
@@ -9882,7 +9954,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>398</v>
       </c>
@@ -9958,7 +10030,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>404</v>
       </c>
@@ -10034,7 +10106,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>405</v>
       </c>
@@ -10110,7 +10182,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>407</v>
       </c>
@@ -10186,7 +10258,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>416</v>
       </c>
@@ -10262,7 +10334,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>421</v>
       </c>
@@ -10338,7 +10410,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>425</v>
       </c>
@@ -10414,7 +10486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>433</v>
       </c>
@@ -10490,7 +10562,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>438</v>
       </c>
@@ -10566,7 +10638,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>444</v>
       </c>
@@ -10642,7 +10714,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>447</v>
       </c>
@@ -10718,7 +10790,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>450</v>
       </c>
@@ -10794,7 +10866,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
         <v>454</v>
       </c>
@@ -10870,7 +10942,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>457</v>
       </c>
@@ -10946,7 +11018,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>462</v>
       </c>
@@ -11022,7 +11094,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>467</v>
       </c>
@@ -11098,7 +11170,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>473</v>
       </c>
@@ -11174,7 +11246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>479</v>
       </c>
@@ -11250,7 +11322,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>484</v>
       </c>
@@ -11326,7 +11398,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>486</v>
       </c>
@@ -11402,7 +11474,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>488</v>
       </c>
@@ -11439,7 +11511,7 @@
         <v>180</v>
       </c>
       <c r="N103" s="4" t="s">
-        <v>30</v>
+        <v>452</v>
       </c>
       <c r="O103" s="5" t="s">
         <v>30</v>
@@ -11478,7 +11550,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>491</v>
       </c>
@@ -11515,7 +11587,7 @@
         <v>267</v>
       </c>
       <c r="N104" s="4" t="s">
-        <v>30</v>
+        <v>1066</v>
       </c>
       <c r="O104" s="5" t="s">
         <v>30</v>
@@ -11554,7 +11626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>493</v>
       </c>
@@ -11630,7 +11702,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>496</v>
       </c>
@@ -11667,7 +11739,7 @@
         <v>231</v>
       </c>
       <c r="N106" s="4" t="s">
-        <v>30</v>
+        <v>1067</v>
       </c>
       <c r="O106" s="5" t="s">
         <v>30</v>
@@ -11706,7 +11778,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>501</v>
       </c>
@@ -11743,7 +11815,7 @@
         <v>180</v>
       </c>
       <c r="N107" s="4" t="s">
-        <v>30</v>
+        <v>1068</v>
       </c>
       <c r="O107" s="5" t="s">
         <v>30</v>
@@ -11782,7 +11854,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>505</v>
       </c>
@@ -11858,7 +11930,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>508</v>
       </c>
@@ -11934,7 +12006,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>266</v>
       </c>
@@ -12010,7 +12082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>516</v>
       </c>
@@ -12084,7 +12156,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="112" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>523</v>
       </c>
@@ -12119,7 +12191,7 @@
         <v>267</v>
       </c>
       <c r="N112" s="4" t="s">
-        <v>30</v>
+        <v>1069</v>
       </c>
       <c r="O112" s="5" t="s">
         <v>30</v>
@@ -12158,7 +12230,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="113" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="s">
         <v>526</v>
       </c>
@@ -12193,7 +12265,7 @@
         <v>1040</v>
       </c>
       <c r="N113" s="4" t="s">
-        <v>30</v>
+        <v>1070</v>
       </c>
       <c r="O113" s="5" t="s">
         <v>30</v>
@@ -12232,7 +12304,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>527</v>
       </c>
@@ -12267,7 +12339,7 @@
         <v>80</v>
       </c>
       <c r="N114" s="4" t="s">
-        <v>30</v>
+        <v>1071</v>
       </c>
       <c r="O114" s="5" t="s">
         <v>30</v>
@@ -12306,7 +12378,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="s">
         <v>532</v>
       </c>
@@ -12380,7 +12452,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>536</v>
       </c>
@@ -12454,7 +12526,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="117" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>542</v>
       </c>
@@ -12528,7 +12600,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="118" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>546</v>
       </c>
@@ -12602,7 +12674,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="119" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>548</v>
       </c>
@@ -12676,7 +12748,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="120" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="s">
         <v>553</v>
       </c>
@@ -12711,7 +12783,7 @@
         <v>148</v>
       </c>
       <c r="N120" s="4" t="s">
-        <v>30</v>
+        <v>1072</v>
       </c>
       <c r="O120" s="5" t="s">
         <v>30</v>
@@ -12750,7 +12822,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>556</v>
       </c>
@@ -12824,7 +12896,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="122" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>560</v>
       </c>
@@ -12859,7 +12931,7 @@
         <v>92</v>
       </c>
       <c r="N122" s="4" t="s">
-        <v>30</v>
+        <v>1073</v>
       </c>
       <c r="O122" s="5" t="s">
         <v>30</v>
@@ -12898,7 +12970,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="s">
         <v>561</v>
       </c>
@@ -12933,7 +13005,7 @@
         <v>564</v>
       </c>
       <c r="N123" s="4" t="s">
-        <v>30</v>
+        <v>1074</v>
       </c>
       <c r="O123" s="5" t="s">
         <v>30</v>
@@ -12972,7 +13044,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>565</v>
       </c>
@@ -13046,7 +13118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="s">
         <v>568</v>
       </c>
@@ -13081,7 +13153,7 @@
         <v>571</v>
       </c>
       <c r="N125" s="4" t="s">
-        <v>30</v>
+        <v>1075</v>
       </c>
       <c r="O125" s="5" t="s">
         <v>30</v>
@@ -13120,7 +13192,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="126" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>572</v>
       </c>
@@ -13155,7 +13227,7 @@
         <v>571</v>
       </c>
       <c r="N126" s="4" t="s">
-        <v>30</v>
+        <v>1076</v>
       </c>
       <c r="O126" s="5" t="s">
         <v>30</v>
@@ -13194,7 +13266,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="5" t="s">
         <v>574</v>
       </c>
@@ -13229,7 +13301,7 @@
         <v>226</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>30</v>
+        <v>1079</v>
       </c>
       <c r="O127" s="5" t="s">
         <v>30</v>
@@ -13268,7 +13340,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="128" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="5" t="s">
         <v>575</v>
       </c>
@@ -13303,7 +13375,7 @@
         <v>226</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>30</v>
+        <v>1080</v>
       </c>
       <c r="O128" s="5" t="s">
         <v>30</v>
@@ -13342,7 +13414,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="129" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="5" t="s">
         <v>576</v>
       </c>
@@ -13377,7 +13449,7 @@
         <v>226</v>
       </c>
       <c r="N129" s="4" t="s">
-        <v>30</v>
+        <v>1077</v>
       </c>
       <c r="O129" s="5" t="s">
         <v>30</v>
@@ -13416,7 +13488,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="130" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>578</v>
       </c>
@@ -13451,7 +13523,7 @@
         <v>226</v>
       </c>
       <c r="N130" s="4" t="s">
-        <v>30</v>
+        <v>1078</v>
       </c>
       <c r="O130" s="5" t="s">
         <v>30</v>
@@ -13490,7 +13562,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="5" t="s">
         <v>579</v>
       </c>
@@ -13564,7 +13636,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="132" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="5" t="s">
         <v>581</v>
       </c>
@@ -13638,7 +13710,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="5" t="s">
         <v>583</v>
       </c>
@@ -13673,7 +13745,7 @@
         <v>586</v>
       </c>
       <c r="N133" s="4" t="s">
-        <v>30</v>
+        <v>1081</v>
       </c>
       <c r="O133" s="5" t="s">
         <v>30</v>
@@ -13712,7 +13784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>587</v>
       </c>
@@ -13786,7 +13858,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="5" t="s">
         <v>589</v>
       </c>
@@ -13860,7 +13932,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>590</v>
       </c>
@@ -13934,7 +14006,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="137" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>596</v>
       </c>
@@ -14008,7 +14080,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>601</v>
       </c>
@@ -14082,7 +14154,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="139" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>605</v>
       </c>
@@ -14156,7 +14228,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="140" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>611</v>
       </c>
@@ -14230,7 +14302,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="141" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>617</v>
       </c>
@@ -14304,7 +14376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="142" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>621</v>
       </c>
@@ -14378,7 +14450,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="143" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>624</v>
       </c>
@@ -14452,7 +14524,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="144" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>628</v>
       </c>
@@ -14487,7 +14559,7 @@
         <v>325</v>
       </c>
       <c r="N144" s="4" t="s">
-        <v>30</v>
+        <v>676</v>
       </c>
       <c r="O144" s="5" t="s">
         <v>30</v>
@@ -14526,7 +14598,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="s">
         <v>629</v>
       </c>
@@ -14561,7 +14633,7 @@
         <v>325</v>
       </c>
       <c r="N145" s="4" t="s">
-        <v>30</v>
+        <v>636</v>
       </c>
       <c r="O145" s="5" t="s">
         <v>30</v>
@@ -14600,7 +14672,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="146" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>631</v>
       </c>
@@ -14635,7 +14707,7 @@
         <v>325</v>
       </c>
       <c r="N146" s="4" t="s">
-        <v>30</v>
+        <v>1082</v>
       </c>
       <c r="O146" s="5" t="s">
         <v>30</v>
@@ -14674,7 +14746,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>632</v>
       </c>
@@ -14748,7 +14820,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>637</v>
       </c>
@@ -14822,7 +14894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="149" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>640</v>
       </c>
@@ -14896,7 +14968,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>643</v>
       </c>
@@ -14970,7 +15042,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>646</v>
       </c>
@@ -15044,7 +15116,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>651</v>
       </c>
@@ -15118,7 +15190,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>655</v>
       </c>
@@ -15192,7 +15264,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>656</v>
       </c>
@@ -15266,7 +15338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>661</v>
       </c>
@@ -15340,7 +15412,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="156" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="5" t="s">
         <v>665</v>
       </c>
@@ -15375,7 +15447,7 @@
         <v>290</v>
       </c>
       <c r="N156" s="4" t="s">
-        <v>30</v>
+        <v>660</v>
       </c>
       <c r="O156" s="5" t="s">
         <v>30</v>
@@ -15414,7 +15486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="157" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="5" t="s">
         <v>667</v>
       </c>
@@ -15449,7 +15521,7 @@
         <v>138</v>
       </c>
       <c r="N157" s="4" t="s">
-        <v>30</v>
+        <v>636</v>
       </c>
       <c r="O157" s="5" t="s">
         <v>30</v>
@@ -15488,7 +15560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="158" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>668</v>
       </c>
@@ -15562,7 +15634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="159" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="5" t="s">
         <v>670</v>
       </c>
@@ -15636,7 +15708,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="5" t="s">
         <v>671</v>
       </c>
@@ -15671,7 +15743,7 @@
         <v>175</v>
       </c>
       <c r="N160" s="4" t="s">
-        <v>30</v>
+        <v>1083</v>
       </c>
       <c r="O160" s="5" t="s">
         <v>30</v>
@@ -15710,7 +15782,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>675</v>
       </c>
@@ -15784,7 +15856,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="162" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
         <v>677</v>
       </c>
@@ -15819,7 +15891,7 @@
         <v>679</v>
       </c>
       <c r="N162" s="4" t="s">
-        <v>30</v>
+        <v>654</v>
       </c>
       <c r="O162" s="5" t="s">
         <v>30</v>
@@ -15858,7 +15930,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="5" t="s">
         <v>680</v>
       </c>
@@ -15893,7 +15965,7 @@
         <v>175</v>
       </c>
       <c r="N163" s="4" t="s">
-        <v>30</v>
+        <v>636</v>
       </c>
       <c r="O163" s="5" t="s">
         <v>30</v>
@@ -15932,7 +16004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="5" t="s">
         <v>682</v>
       </c>
@@ -15967,7 +16039,7 @@
         <v>420</v>
       </c>
       <c r="N164" s="4" t="s">
-        <v>30</v>
+        <v>1084</v>
       </c>
       <c r="O164" s="5" t="s">
         <v>30</v>
@@ -16006,7 +16078,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="165" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="5" t="s">
         <v>684</v>
       </c>
@@ -16041,7 +16113,7 @@
         <v>1043</v>
       </c>
       <c r="N165" s="4" t="s">
-        <v>30</v>
+        <v>654</v>
       </c>
       <c r="O165" s="5" t="s">
         <v>30</v>
@@ -16080,7 +16152,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="166" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
         <v>685</v>
       </c>
@@ -16154,7 +16226,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>686</v>
       </c>
@@ -16228,7 +16300,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="168" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>690</v>
       </c>
@@ -16302,7 +16374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="5" t="s">
         <v>694</v>
       </c>
@@ -16376,7 +16448,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="5" t="s">
         <v>696</v>
       </c>
@@ -16450,7 +16522,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>697</v>
       </c>
@@ -16524,7 +16596,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>700</v>
       </c>
@@ -16598,7 +16670,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="173" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="5" t="s">
         <v>701</v>
       </c>
@@ -16672,7 +16744,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="5" t="s">
         <v>703</v>
       </c>
@@ -16746,7 +16818,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>706</v>
       </c>
@@ -16820,7 +16892,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="176" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>709</v>
       </c>
@@ -16894,7 +16966,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="5" t="s">
         <v>713</v>
       </c>
@@ -16929,7 +17001,7 @@
         <v>717</v>
       </c>
       <c r="N177" s="4" t="s">
-        <v>30</v>
+        <v>1085</v>
       </c>
       <c r="O177" s="5" t="s">
         <v>30</v>
@@ -16968,7 +17040,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="5" t="s">
         <v>718</v>
       </c>
@@ -17042,7 +17114,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="179" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>720</v>
       </c>
@@ -17116,7 +17188,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>725</v>
       </c>
@@ -17190,7 +17262,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>731</v>
       </c>
@@ -17264,7 +17336,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="182" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>736</v>
       </c>
@@ -17299,7 +17371,7 @@
         <v>238</v>
       </c>
       <c r="N182" s="4" t="s">
-        <v>30</v>
+        <v>1086</v>
       </c>
       <c r="O182" s="5" t="s">
         <v>30</v>
@@ -17338,7 +17410,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="5" t="s">
         <v>738</v>
       </c>
@@ -17412,2458 +17484,2459 @@
         <v>30</v>
       </c>
     </row>
-    <row r="184" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B184" s="2"/>
     </row>
-    <row r="185" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B185" s="2"/>
     </row>
-    <row r="186" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B186" s="2"/>
     </row>
-    <row r="187" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B187" s="2"/>
     </row>
-    <row r="188" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B188" s="2"/>
     </row>
-    <row r="189" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B189" s="2"/>
     </row>
-    <row r="190" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B190" s="2"/>
     </row>
-    <row r="191" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B191" s="2"/>
     </row>
-    <row r="192" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B192" s="2"/>
     </row>
-    <row r="193" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B193" s="2"/>
     </row>
-    <row r="194" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B194" s="2"/>
     </row>
-    <row r="195" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B195" s="2"/>
     </row>
-    <row r="196" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B196" s="2"/>
     </row>
-    <row r="197" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B197" s="2"/>
     </row>
-    <row r="198" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B198" s="2"/>
     </row>
-    <row r="199" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B199" s="2"/>
     </row>
-    <row r="200" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B200" s="2"/>
     </row>
-    <row r="201" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B201" s="2"/>
     </row>
-    <row r="202" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B202" s="2"/>
     </row>
-    <row r="203" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B203" s="2"/>
     </row>
-    <row r="204" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B204" s="2"/>
     </row>
-    <row r="205" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B205" s="2"/>
     </row>
-    <row r="206" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B206" s="2"/>
     </row>
-    <row r="207" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B207" s="2"/>
     </row>
-    <row r="208" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B208" s="2"/>
     </row>
-    <row r="209" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B209" s="2"/>
     </row>
-    <row r="210" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B210" s="2"/>
     </row>
-    <row r="211" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B211" s="2"/>
     </row>
-    <row r="212" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B212" s="2"/>
     </row>
-    <row r="213" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B213" s="2"/>
     </row>
-    <row r="214" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B214" s="2"/>
     </row>
-    <row r="215" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B215" s="2"/>
     </row>
-    <row r="216" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B216" s="2"/>
     </row>
-    <row r="217" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B217" s="2"/>
     </row>
-    <row r="218" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B218" s="2"/>
     </row>
-    <row r="219" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B219" s="2"/>
     </row>
-    <row r="220" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B220" s="2"/>
     </row>
-    <row r="221" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B221" s="2"/>
     </row>
-    <row r="222" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B222" s="2"/>
     </row>
-    <row r="223" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B223" s="2"/>
     </row>
-    <row r="224" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B224" s="2"/>
     </row>
-    <row r="225" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B225" s="2"/>
     </row>
-    <row r="226" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B226" s="2"/>
     </row>
-    <row r="227" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B227" s="2"/>
     </row>
-    <row r="228" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B228" s="2"/>
     </row>
-    <row r="229" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B229" s="2"/>
     </row>
-    <row r="230" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B230" s="2"/>
     </row>
-    <row r="231" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B231" s="2"/>
     </row>
-    <row r="232" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B232" s="2"/>
     </row>
-    <row r="233" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B233" s="2"/>
     </row>
-    <row r="234" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B234" s="2"/>
     </row>
-    <row r="235" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B235" s="2"/>
     </row>
-    <row r="236" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B236" s="2"/>
     </row>
-    <row r="237" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B237" s="2"/>
     </row>
-    <row r="238" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B238" s="2"/>
     </row>
-    <row r="239" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B239" s="2"/>
     </row>
-    <row r="240" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B240" s="2"/>
     </row>
-    <row r="241" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B241" s="2"/>
     </row>
-    <row r="242" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B242" s="2"/>
     </row>
-    <row r="243" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B243" s="2"/>
     </row>
-    <row r="244" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B244" s="2"/>
     </row>
-    <row r="245" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B245" s="2"/>
     </row>
-    <row r="246" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B246" s="2"/>
     </row>
-    <row r="247" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B247" s="2"/>
     </row>
-    <row r="248" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B248" s="2"/>
     </row>
-    <row r="249" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B249" s="2"/>
     </row>
-    <row r="250" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B250" s="2"/>
     </row>
-    <row r="251" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B251" s="2"/>
     </row>
-    <row r="252" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B252" s="2"/>
     </row>
-    <row r="253" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B253" s="2"/>
     </row>
-    <row r="254" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B254" s="2"/>
     </row>
-    <row r="255" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B255" s="2"/>
     </row>
-    <row r="256" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B256" s="2"/>
     </row>
-    <row r="257" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B257" s="2"/>
     </row>
-    <row r="258" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B258" s="2"/>
     </row>
-    <row r="259" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B259" s="2"/>
     </row>
-    <row r="260" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B260" s="2"/>
     </row>
-    <row r="261" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B261" s="2"/>
     </row>
-    <row r="262" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B262" s="2"/>
     </row>
-    <row r="263" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B263" s="2"/>
     </row>
-    <row r="264" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B264" s="2"/>
     </row>
-    <row r="265" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B265" s="2"/>
     </row>
-    <row r="266" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B266" s="2"/>
     </row>
-    <row r="267" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B267" s="2"/>
     </row>
-    <row r="268" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B268" s="2"/>
     </row>
-    <row r="269" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B269" s="2"/>
     </row>
-    <row r="270" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B270" s="2"/>
     </row>
-    <row r="271" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B271" s="2"/>
     </row>
-    <row r="272" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B272" s="2"/>
     </row>
-    <row r="273" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B273" s="2"/>
     </row>
-    <row r="274" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B274" s="2"/>
     </row>
-    <row r="275" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B275" s="2"/>
     </row>
-    <row r="276" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B276" s="2"/>
     </row>
-    <row r="277" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B277" s="2"/>
     </row>
-    <row r="278" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B278" s="2"/>
     </row>
-    <row r="279" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B279" s="2"/>
     </row>
-    <row r="280" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B280" s="2"/>
     </row>
-    <row r="281" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B281" s="2"/>
     </row>
-    <row r="282" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B282" s="2"/>
     </row>
-    <row r="283" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B283" s="2"/>
     </row>
-    <row r="284" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B284" s="2"/>
     </row>
-    <row r="285" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B285" s="2"/>
     </row>
-    <row r="286" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B286" s="2"/>
     </row>
-    <row r="287" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B287" s="2"/>
     </row>
-    <row r="288" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B288" s="2"/>
     </row>
-    <row r="289" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B289" s="2"/>
     </row>
-    <row r="290" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B290" s="2"/>
     </row>
-    <row r="291" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B291" s="2"/>
     </row>
-    <row r="292" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B292" s="2"/>
     </row>
-    <row r="293" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B293" s="2"/>
     </row>
-    <row r="294" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B294" s="2"/>
     </row>
-    <row r="295" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B295" s="2"/>
     </row>
-    <row r="296" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B296" s="2"/>
     </row>
-    <row r="297" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B297" s="2"/>
     </row>
-    <row r="298" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B298" s="2"/>
     </row>
-    <row r="299" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B299" s="2"/>
     </row>
-    <row r="300" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B300" s="2"/>
     </row>
-    <row r="301" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B301" s="2"/>
     </row>
-    <row r="302" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B302" s="2"/>
     </row>
-    <row r="303" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B303" s="2"/>
     </row>
-    <row r="304" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B304" s="2"/>
     </row>
-    <row r="305" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B305" s="2"/>
     </row>
-    <row r="306" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B306" s="2"/>
     </row>
-    <row r="307" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B307" s="2"/>
     </row>
-    <row r="308" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B308" s="2"/>
     </row>
-    <row r="309" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B309" s="2"/>
     </row>
-    <row r="310" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B310" s="2"/>
     </row>
-    <row r="311" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B311" s="2"/>
     </row>
-    <row r="312" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B312" s="2"/>
     </row>
-    <row r="313" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B313" s="2"/>
     </row>
-    <row r="314" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B314" s="2"/>
     </row>
-    <row r="315" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B315" s="2"/>
     </row>
-    <row r="316" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B316" s="2"/>
     </row>
-    <row r="317" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B317" s="2"/>
     </row>
-    <row r="318" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B318" s="2"/>
     </row>
-    <row r="319" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B319" s="2"/>
     </row>
-    <row r="320" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B320" s="2"/>
     </row>
-    <row r="321" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B321" s="2"/>
     </row>
-    <row r="322" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B322" s="2"/>
     </row>
-    <row r="323" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B323" s="2"/>
     </row>
-    <row r="324" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B324" s="2"/>
     </row>
-    <row r="325" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B325" s="2"/>
     </row>
-    <row r="326" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B326" s="2"/>
     </row>
-    <row r="327" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B327" s="2"/>
     </row>
-    <row r="328" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B328" s="2"/>
     </row>
-    <row r="329" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B329" s="2"/>
     </row>
-    <row r="330" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B330" s="2"/>
     </row>
-    <row r="331" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B331" s="2"/>
     </row>
-    <row r="332" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B332" s="2"/>
     </row>
-    <row r="333" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B333" s="2"/>
     </row>
-    <row r="334" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B334" s="2"/>
     </row>
-    <row r="335" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B335" s="2"/>
     </row>
-    <row r="336" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B336" s="2"/>
     </row>
-    <row r="337" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B337" s="2"/>
     </row>
-    <row r="338" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B338" s="2"/>
     </row>
-    <row r="339" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B339" s="2"/>
     </row>
-    <row r="340" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B340" s="2"/>
     </row>
-    <row r="341" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B341" s="2"/>
     </row>
-    <row r="342" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B342" s="2"/>
     </row>
-    <row r="343" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B343" s="2"/>
     </row>
-    <row r="344" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B344" s="2"/>
     </row>
-    <row r="345" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B345" s="2"/>
     </row>
-    <row r="346" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B346" s="2"/>
     </row>
-    <row r="347" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B347" s="2"/>
     </row>
-    <row r="348" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B348" s="2"/>
     </row>
-    <row r="349" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B349" s="2"/>
     </row>
-    <row r="350" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B350" s="2"/>
     </row>
-    <row r="351" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B351" s="2"/>
     </row>
-    <row r="352" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B352" s="2"/>
     </row>
-    <row r="353" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B353" s="2"/>
     </row>
-    <row r="354" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B354" s="2"/>
     </row>
-    <row r="355" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B355" s="2"/>
     </row>
-    <row r="356" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B356" s="2"/>
     </row>
-    <row r="357" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B357" s="2"/>
     </row>
-    <row r="358" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B358" s="2"/>
     </row>
-    <row r="359" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B359" s="2"/>
     </row>
-    <row r="360" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B360" s="2"/>
     </row>
-    <row r="361" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B361" s="2"/>
     </row>
-    <row r="362" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B362" s="2"/>
     </row>
-    <row r="363" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B363" s="2"/>
     </row>
-    <row r="364" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B364" s="2"/>
     </row>
-    <row r="365" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B365" s="2"/>
     </row>
-    <row r="366" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B366" s="2"/>
     </row>
-    <row r="367" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B367" s="2"/>
     </row>
-    <row r="368" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B368" s="2"/>
     </row>
-    <row r="369" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B369" s="2"/>
     </row>
-    <row r="370" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B370" s="2"/>
     </row>
-    <row r="371" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B371" s="2"/>
     </row>
-    <row r="372" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B372" s="2"/>
     </row>
-    <row r="373" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B373" s="2"/>
     </row>
-    <row r="374" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B374" s="2"/>
     </row>
-    <row r="375" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B375" s="2"/>
     </row>
-    <row r="376" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B376" s="2"/>
     </row>
-    <row r="377" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B377" s="2"/>
     </row>
-    <row r="378" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B378" s="2"/>
     </row>
-    <row r="379" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B379" s="2"/>
     </row>
-    <row r="380" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B380" s="2"/>
     </row>
-    <row r="381" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B381" s="2"/>
     </row>
-    <row r="382" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B382" s="2"/>
     </row>
-    <row r="383" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B383" s="2"/>
     </row>
-    <row r="384" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B384" s="2"/>
     </row>
-    <row r="385" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B385" s="2"/>
     </row>
-    <row r="386" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B386" s="2"/>
     </row>
-    <row r="387" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B387" s="2"/>
     </row>
-    <row r="388" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B388" s="2"/>
     </row>
-    <row r="389" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B389" s="2"/>
     </row>
-    <row r="390" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B390" s="2"/>
     </row>
-    <row r="391" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B391" s="2"/>
     </row>
-    <row r="392" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B392" s="2"/>
     </row>
-    <row r="393" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B393" s="2"/>
     </row>
-    <row r="394" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B394" s="2"/>
     </row>
-    <row r="395" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B395" s="2"/>
     </row>
-    <row r="396" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B396" s="2"/>
     </row>
-    <row r="397" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B397" s="2"/>
     </row>
-    <row r="398" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B398" s="2"/>
     </row>
-    <row r="399" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B399" s="2"/>
     </row>
-    <row r="400" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B400" s="2"/>
     </row>
-    <row r="401" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B401" s="2"/>
     </row>
-    <row r="402" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B402" s="2"/>
     </row>
-    <row r="403" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B403" s="2"/>
     </row>
-    <row r="404" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B404" s="2"/>
     </row>
-    <row r="405" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B405" s="2"/>
     </row>
-    <row r="406" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B406" s="2"/>
     </row>
-    <row r="407" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B407" s="2"/>
     </row>
-    <row r="408" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B408" s="2"/>
     </row>
-    <row r="409" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B409" s="2"/>
     </row>
-    <row r="410" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B410" s="2"/>
     </row>
-    <row r="411" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B411" s="2"/>
     </row>
-    <row r="412" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B412" s="2"/>
     </row>
-    <row r="413" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B413" s="2"/>
     </row>
-    <row r="414" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B414" s="2"/>
     </row>
-    <row r="415" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B415" s="2"/>
     </row>
-    <row r="416" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B416" s="2"/>
     </row>
-    <row r="417" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B417" s="2"/>
     </row>
-    <row r="418" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B418" s="2"/>
     </row>
-    <row r="419" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B419" s="2"/>
     </row>
-    <row r="420" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B420" s="2"/>
     </row>
-    <row r="421" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B421" s="2"/>
     </row>
-    <row r="422" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B422" s="2"/>
     </row>
-    <row r="423" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B423" s="2"/>
     </row>
-    <row r="424" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B424" s="2"/>
     </row>
-    <row r="425" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B425" s="2"/>
     </row>
-    <row r="426" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B426" s="2"/>
     </row>
-    <row r="427" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B427" s="2"/>
     </row>
-    <row r="428" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B428" s="2"/>
     </row>
-    <row r="429" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B429" s="2"/>
     </row>
-    <row r="430" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B430" s="2"/>
     </row>
-    <row r="431" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B431" s="2"/>
     </row>
-    <row r="432" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B432" s="2"/>
     </row>
-    <row r="433" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B433" s="2"/>
     </row>
-    <row r="434" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B434" s="2"/>
     </row>
-    <row r="435" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B435" s="2"/>
     </row>
-    <row r="436" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B436" s="2"/>
     </row>
-    <row r="437" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B437" s="2"/>
     </row>
-    <row r="438" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B438" s="2"/>
     </row>
-    <row r="439" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B439" s="2"/>
     </row>
-    <row r="440" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B440" s="2"/>
     </row>
-    <row r="441" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B441" s="2"/>
     </row>
-    <row r="442" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B442" s="2"/>
     </row>
-    <row r="443" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B443" s="2"/>
     </row>
-    <row r="444" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B444" s="2"/>
     </row>
-    <row r="445" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B445" s="2"/>
     </row>
-    <row r="446" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B446" s="2"/>
     </row>
-    <row r="447" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B447" s="2"/>
     </row>
-    <row r="448" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B448" s="2"/>
     </row>
-    <row r="449" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B449" s="2"/>
     </row>
-    <row r="450" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B450" s="2"/>
     </row>
-    <row r="451" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B451" s="2"/>
     </row>
-    <row r="452" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B452" s="2"/>
     </row>
-    <row r="453" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B453" s="2"/>
     </row>
-    <row r="454" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B454" s="2"/>
     </row>
-    <row r="455" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B455" s="2"/>
     </row>
-    <row r="456" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B456" s="2"/>
     </row>
-    <row r="457" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B457" s="2"/>
     </row>
-    <row r="458" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B458" s="2"/>
     </row>
-    <row r="459" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B459" s="2"/>
     </row>
-    <row r="460" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B460" s="2"/>
     </row>
-    <row r="461" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B461" s="2"/>
     </row>
-    <row r="462" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B462" s="2"/>
     </row>
-    <row r="463" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B463" s="2"/>
     </row>
-    <row r="464" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B464" s="2"/>
     </row>
-    <row r="465" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B465" s="2"/>
     </row>
-    <row r="466" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B466" s="2"/>
     </row>
-    <row r="467" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B467" s="2"/>
     </row>
-    <row r="468" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B468" s="2"/>
     </row>
-    <row r="469" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B469" s="2"/>
     </row>
-    <row r="470" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B470" s="2"/>
     </row>
-    <row r="471" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B471" s="2"/>
     </row>
-    <row r="472" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B472" s="2"/>
     </row>
-    <row r="473" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B473" s="2"/>
     </row>
-    <row r="474" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B474" s="2"/>
     </row>
-    <row r="475" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B475" s="2"/>
     </row>
-    <row r="476" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B476" s="2"/>
     </row>
-    <row r="477" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B477" s="2"/>
     </row>
-    <row r="478" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B478" s="2"/>
     </row>
-    <row r="479" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B479" s="2"/>
     </row>
-    <row r="480" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B480" s="2"/>
     </row>
-    <row r="481" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B481" s="2"/>
     </row>
-    <row r="482" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B482" s="2"/>
     </row>
-    <row r="483" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B483" s="2"/>
     </row>
-    <row r="484" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B484" s="2"/>
     </row>
-    <row r="485" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B485" s="2"/>
     </row>
-    <row r="486" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B486" s="2"/>
     </row>
-    <row r="487" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B487" s="2"/>
     </row>
-    <row r="488" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B488" s="2"/>
     </row>
-    <row r="489" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B489" s="2"/>
     </row>
-    <row r="490" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B490" s="2"/>
     </row>
-    <row r="491" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B491" s="2"/>
     </row>
-    <row r="492" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B492" s="2"/>
     </row>
-    <row r="493" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B493" s="2"/>
     </row>
-    <row r="494" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B494" s="2"/>
     </row>
-    <row r="495" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B495" s="2"/>
     </row>
-    <row r="496" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B496" s="2"/>
     </row>
-    <row r="497" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B497" s="2"/>
     </row>
-    <row r="498" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B498" s="2"/>
     </row>
-    <row r="499" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B499" s="2"/>
     </row>
-    <row r="500" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B500" s="2"/>
     </row>
-    <row r="501" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B501" s="2"/>
     </row>
-    <row r="502" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B502" s="2"/>
     </row>
-    <row r="503" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B503" s="2"/>
     </row>
-    <row r="504" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B504" s="2"/>
     </row>
-    <row r="505" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B505" s="2"/>
     </row>
-    <row r="506" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B506" s="2"/>
     </row>
-    <row r="507" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B507" s="2"/>
     </row>
-    <row r="508" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B508" s="2"/>
     </row>
-    <row r="509" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B509" s="2"/>
     </row>
-    <row r="510" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B510" s="2"/>
     </row>
-    <row r="511" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B511" s="2"/>
     </row>
-    <row r="512" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B512" s="2"/>
     </row>
-    <row r="513" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B513" s="2"/>
     </row>
-    <row r="514" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B514" s="2"/>
     </row>
-    <row r="515" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B515" s="2"/>
     </row>
-    <row r="516" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B516" s="2"/>
     </row>
-    <row r="517" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B517" s="2"/>
     </row>
-    <row r="518" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B518" s="2"/>
     </row>
-    <row r="519" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B519" s="2"/>
     </row>
-    <row r="520" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B520" s="2"/>
     </row>
-    <row r="521" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B521" s="2"/>
     </row>
-    <row r="522" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B522" s="2"/>
     </row>
-    <row r="523" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B523" s="2"/>
     </row>
-    <row r="524" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B524" s="2"/>
     </row>
-    <row r="525" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B525" s="2"/>
     </row>
-    <row r="526" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B526" s="2"/>
     </row>
-    <row r="527" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B527" s="2"/>
     </row>
-    <row r="528" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B528" s="2"/>
     </row>
-    <row r="529" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B529" s="2"/>
     </row>
-    <row r="530" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B530" s="2"/>
     </row>
-    <row r="531" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B531" s="2"/>
     </row>
-    <row r="532" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B532" s="2"/>
     </row>
-    <row r="533" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B533" s="2"/>
     </row>
-    <row r="534" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B534" s="2"/>
     </row>
-    <row r="535" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B535" s="2"/>
     </row>
-    <row r="536" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B536" s="2"/>
     </row>
-    <row r="537" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B537" s="2"/>
     </row>
-    <row r="538" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B538" s="2"/>
     </row>
-    <row r="539" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B539" s="2"/>
     </row>
-    <row r="540" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B540" s="2"/>
     </row>
-    <row r="541" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B541" s="2"/>
     </row>
-    <row r="542" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B542" s="2"/>
     </row>
-    <row r="543" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B543" s="2"/>
     </row>
-    <row r="544" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B544" s="2"/>
     </row>
-    <row r="545" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B545" s="2"/>
     </row>
-    <row r="546" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B546" s="2"/>
     </row>
-    <row r="547" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B547" s="2"/>
     </row>
-    <row r="548" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B548" s="2"/>
     </row>
-    <row r="549" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B549" s="2"/>
     </row>
-    <row r="550" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B550" s="2"/>
     </row>
-    <row r="551" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B551" s="2"/>
     </row>
-    <row r="552" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B552" s="2"/>
     </row>
-    <row r="553" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B553" s="2"/>
     </row>
-    <row r="554" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B554" s="2"/>
     </row>
-    <row r="555" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B555" s="2"/>
     </row>
-    <row r="556" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B556" s="2"/>
     </row>
-    <row r="557" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B557" s="2"/>
     </row>
-    <row r="558" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B558" s="2"/>
     </row>
-    <row r="559" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B559" s="2"/>
     </row>
-    <row r="560" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B560" s="2"/>
     </row>
-    <row r="561" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B561" s="2"/>
     </row>
-    <row r="562" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B562" s="2"/>
     </row>
-    <row r="563" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B563" s="2"/>
     </row>
-    <row r="564" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B564" s="2"/>
     </row>
-    <row r="565" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B565" s="2"/>
     </row>
-    <row r="566" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B566" s="2"/>
     </row>
-    <row r="567" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B567" s="2"/>
     </row>
-    <row r="568" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B568" s="2"/>
     </row>
-    <row r="569" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B569" s="2"/>
     </row>
-    <row r="570" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B570" s="2"/>
     </row>
-    <row r="571" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B571" s="2"/>
     </row>
-    <row r="572" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B572" s="2"/>
     </row>
-    <row r="573" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B573" s="2"/>
     </row>
-    <row r="574" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B574" s="2"/>
     </row>
-    <row r="575" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B575" s="2"/>
     </row>
-    <row r="576" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B576" s="2"/>
     </row>
-    <row r="577" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B577" s="2"/>
     </row>
-    <row r="578" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B578" s="2"/>
     </row>
-    <row r="579" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B579" s="2"/>
     </row>
-    <row r="580" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B580" s="2"/>
     </row>
-    <row r="581" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B581" s="2"/>
     </row>
-    <row r="582" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B582" s="2"/>
     </row>
-    <row r="583" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B583" s="2"/>
     </row>
-    <row r="584" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B584" s="2"/>
     </row>
-    <row r="585" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B585" s="2"/>
     </row>
-    <row r="586" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B586" s="2"/>
     </row>
-    <row r="587" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B587" s="2"/>
     </row>
-    <row r="588" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B588" s="2"/>
     </row>
-    <row r="589" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B589" s="2"/>
     </row>
-    <row r="590" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B590" s="2"/>
     </row>
-    <row r="591" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B591" s="2"/>
     </row>
-    <row r="592" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B592" s="2"/>
     </row>
-    <row r="593" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B593" s="2"/>
     </row>
-    <row r="594" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B594" s="2"/>
     </row>
-    <row r="595" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B595" s="2"/>
     </row>
-    <row r="596" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B596" s="2"/>
     </row>
-    <row r="597" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B597" s="2"/>
     </row>
-    <row r="598" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B598" s="2"/>
     </row>
-    <row r="599" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B599" s="2"/>
     </row>
-    <row r="600" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B600" s="2"/>
     </row>
-    <row r="601" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B601" s="2"/>
     </row>
-    <row r="602" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B602" s="2"/>
     </row>
-    <row r="603" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B603" s="2"/>
     </row>
-    <row r="604" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B604" s="2"/>
     </row>
-    <row r="605" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B605" s="2"/>
     </row>
-    <row r="606" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B606" s="2"/>
     </row>
-    <row r="607" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B607" s="2"/>
     </row>
-    <row r="608" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B608" s="2"/>
     </row>
-    <row r="609" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B609" s="2"/>
     </row>
-    <row r="610" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B610" s="2"/>
     </row>
-    <row r="611" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B611" s="2"/>
     </row>
-    <row r="612" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B612" s="2"/>
     </row>
-    <row r="613" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B613" s="2"/>
     </row>
-    <row r="614" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B614" s="2"/>
     </row>
-    <row r="615" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B615" s="2"/>
     </row>
-    <row r="616" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B616" s="2"/>
     </row>
-    <row r="617" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B617" s="2"/>
     </row>
-    <row r="618" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B618" s="2"/>
     </row>
-    <row r="619" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B619" s="2"/>
     </row>
-    <row r="620" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B620" s="2"/>
     </row>
-    <row r="621" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B621" s="2"/>
     </row>
-    <row r="622" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B622" s="2"/>
     </row>
-    <row r="623" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B623" s="2"/>
     </row>
-    <row r="624" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B624" s="2"/>
     </row>
-    <row r="625" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B625" s="2"/>
     </row>
-    <row r="626" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B626" s="2"/>
     </row>
-    <row r="627" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B627" s="2"/>
     </row>
-    <row r="628" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B628" s="2"/>
     </row>
-    <row r="629" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B629" s="2"/>
     </row>
-    <row r="630" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B630" s="2"/>
     </row>
-    <row r="631" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B631" s="2"/>
     </row>
-    <row r="632" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B632" s="2"/>
     </row>
-    <row r="633" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B633" s="2"/>
     </row>
-    <row r="634" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B634" s="2"/>
     </row>
-    <row r="635" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B635" s="2"/>
     </row>
-    <row r="636" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B636" s="2"/>
     </row>
-    <row r="637" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B637" s="2"/>
     </row>
-    <row r="638" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B638" s="2"/>
     </row>
-    <row r="639" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B639" s="2"/>
     </row>
-    <row r="640" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B640" s="2"/>
     </row>
-    <row r="641" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B641" s="2"/>
     </row>
-    <row r="642" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B642" s="2"/>
     </row>
-    <row r="643" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B643" s="2"/>
     </row>
-    <row r="644" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B644" s="2"/>
     </row>
-    <row r="645" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B645" s="2"/>
     </row>
-    <row r="646" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B646" s="2"/>
     </row>
-    <row r="647" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B647" s="2"/>
     </row>
-    <row r="648" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B648" s="2"/>
     </row>
-    <row r="649" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B649" s="2"/>
     </row>
-    <row r="650" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B650" s="2"/>
     </row>
-    <row r="651" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B651" s="2"/>
     </row>
-    <row r="652" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B652" s="2"/>
     </row>
-    <row r="653" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B653" s="2"/>
     </row>
-    <row r="654" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B654" s="2"/>
     </row>
-    <row r="655" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B655" s="2"/>
     </row>
-    <row r="656" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B656" s="2"/>
     </row>
-    <row r="657" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B657" s="2"/>
     </row>
-    <row r="658" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B658" s="2"/>
     </row>
-    <row r="659" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B659" s="2"/>
     </row>
-    <row r="660" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B660" s="2"/>
     </row>
-    <row r="661" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B661" s="2"/>
     </row>
-    <row r="662" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B662" s="2"/>
     </row>
-    <row r="663" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B663" s="2"/>
     </row>
-    <row r="664" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B664" s="2"/>
     </row>
-    <row r="665" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B665" s="2"/>
     </row>
-    <row r="666" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B666" s="2"/>
     </row>
-    <row r="667" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B667" s="2"/>
     </row>
-    <row r="668" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B668" s="2"/>
     </row>
-    <row r="669" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B669" s="2"/>
     </row>
-    <row r="670" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B670" s="2"/>
     </row>
-    <row r="671" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B671" s="2"/>
     </row>
-    <row r="672" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B672" s="2"/>
     </row>
-    <row r="673" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B673" s="2"/>
     </row>
-    <row r="674" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B674" s="2"/>
     </row>
-    <row r="675" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B675" s="2"/>
     </row>
-    <row r="676" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B676" s="2"/>
     </row>
-    <row r="677" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B677" s="2"/>
     </row>
-    <row r="678" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B678" s="2"/>
     </row>
-    <row r="679" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B679" s="2"/>
     </row>
-    <row r="680" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B680" s="2"/>
     </row>
-    <row r="681" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B681" s="2"/>
     </row>
-    <row r="682" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B682" s="2"/>
     </row>
-    <row r="683" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B683" s="2"/>
     </row>
-    <row r="684" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B684" s="2"/>
     </row>
-    <row r="685" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B685" s="2"/>
     </row>
-    <row r="686" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B686" s="2"/>
     </row>
-    <row r="687" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B687" s="2"/>
     </row>
-    <row r="688" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B688" s="2"/>
     </row>
-    <row r="689" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B689" s="2"/>
     </row>
-    <row r="690" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B690" s="2"/>
     </row>
-    <row r="691" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B691" s="2"/>
     </row>
-    <row r="692" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B692" s="2"/>
     </row>
-    <row r="693" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B693" s="2"/>
     </row>
-    <row r="694" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B694" s="2"/>
     </row>
-    <row r="695" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B695" s="2"/>
     </row>
-    <row r="696" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B696" s="2"/>
     </row>
-    <row r="697" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B697" s="2"/>
     </row>
-    <row r="698" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B698" s="2"/>
     </row>
-    <row r="699" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B699" s="2"/>
     </row>
-    <row r="700" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B700" s="2"/>
     </row>
-    <row r="701" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B701" s="2"/>
     </row>
-    <row r="702" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B702" s="2"/>
     </row>
-    <row r="703" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B703" s="2"/>
     </row>
-    <row r="704" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B704" s="2"/>
     </row>
-    <row r="705" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B705" s="2"/>
     </row>
-    <row r="706" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B706" s="2"/>
     </row>
-    <row r="707" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B707" s="2"/>
     </row>
-    <row r="708" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B708" s="2"/>
     </row>
-    <row r="709" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B709" s="2"/>
     </row>
-    <row r="710" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B710" s="2"/>
     </row>
-    <row r="711" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B711" s="2"/>
     </row>
-    <row r="712" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B712" s="2"/>
     </row>
-    <row r="713" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B713" s="2"/>
     </row>
-    <row r="714" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B714" s="2"/>
     </row>
-    <row r="715" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B715" s="2"/>
     </row>
-    <row r="716" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B716" s="2"/>
     </row>
-    <row r="717" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B717" s="2"/>
     </row>
-    <row r="718" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B718" s="2"/>
     </row>
-    <row r="719" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B719" s="2"/>
     </row>
-    <row r="720" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B720" s="2"/>
     </row>
-    <row r="721" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B721" s="2"/>
     </row>
-    <row r="722" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B722" s="2"/>
     </row>
-    <row r="723" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B723" s="2"/>
     </row>
-    <row r="724" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B724" s="2"/>
     </row>
-    <row r="725" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B725" s="2"/>
     </row>
-    <row r="726" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B726" s="2"/>
     </row>
-    <row r="727" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B727" s="2"/>
     </row>
-    <row r="728" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B728" s="2"/>
     </row>
-    <row r="729" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B729" s="2"/>
     </row>
-    <row r="730" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B730" s="2"/>
     </row>
-    <row r="731" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B731" s="2"/>
     </row>
-    <row r="732" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B732" s="2"/>
     </row>
-    <row r="733" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B733" s="2"/>
     </row>
-    <row r="734" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B734" s="2"/>
     </row>
-    <row r="735" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B735" s="2"/>
     </row>
-    <row r="736" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B736" s="2"/>
     </row>
-    <row r="737" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B737" s="2"/>
     </row>
-    <row r="738" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B738" s="2"/>
     </row>
-    <row r="739" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B739" s="2"/>
     </row>
-    <row r="740" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B740" s="2"/>
     </row>
-    <row r="741" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B741" s="2"/>
     </row>
-    <row r="742" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B742" s="2"/>
     </row>
-    <row r="743" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B743" s="2"/>
     </row>
-    <row r="744" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B744" s="2"/>
     </row>
-    <row r="745" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B745" s="2"/>
     </row>
-    <row r="746" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B746" s="2"/>
     </row>
-    <row r="747" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B747" s="2"/>
     </row>
-    <row r="748" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B748" s="2"/>
     </row>
-    <row r="749" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B749" s="2"/>
     </row>
-    <row r="750" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B750" s="2"/>
     </row>
-    <row r="751" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B751" s="2"/>
     </row>
-    <row r="752" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B752" s="2"/>
     </row>
-    <row r="753" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B753" s="2"/>
     </row>
-    <row r="754" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B754" s="2"/>
     </row>
-    <row r="755" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B755" s="2"/>
     </row>
-    <row r="756" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B756" s="2"/>
     </row>
-    <row r="757" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B757" s="2"/>
     </row>
-    <row r="758" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B758" s="2"/>
     </row>
-    <row r="759" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B759" s="2"/>
     </row>
-    <row r="760" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B760" s="2"/>
     </row>
-    <row r="761" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B761" s="2"/>
     </row>
-    <row r="762" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B762" s="2"/>
     </row>
-    <row r="763" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B763" s="2"/>
     </row>
-    <row r="764" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B764" s="2"/>
     </row>
-    <row r="765" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B765" s="2"/>
     </row>
-    <row r="766" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B766" s="2"/>
     </row>
-    <row r="767" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B767" s="2"/>
     </row>
-    <row r="768" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B768" s="2"/>
     </row>
-    <row r="769" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B769" s="2"/>
     </row>
-    <row r="770" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B770" s="2"/>
     </row>
-    <row r="771" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B771" s="2"/>
     </row>
-    <row r="772" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B772" s="2"/>
     </row>
-    <row r="773" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B773" s="2"/>
     </row>
-    <row r="774" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="774" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B774" s="2"/>
     </row>
-    <row r="775" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B775" s="2"/>
     </row>
-    <row r="776" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B776" s="2"/>
     </row>
-    <row r="777" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B777" s="2"/>
     </row>
-    <row r="778" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B778" s="2"/>
     </row>
-    <row r="779" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B779" s="2"/>
     </row>
-    <row r="780" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B780" s="2"/>
     </row>
-    <row r="781" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B781" s="2"/>
     </row>
-    <row r="782" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="782" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B782" s="2"/>
     </row>
-    <row r="783" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="783" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B783" s="2"/>
     </row>
-    <row r="784" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="784" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B784" s="2"/>
     </row>
-    <row r="785" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="785" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B785" s="2"/>
     </row>
-    <row r="786" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="786" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B786" s="2"/>
     </row>
-    <row r="787" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="787" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B787" s="2"/>
     </row>
-    <row r="788" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="788" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B788" s="2"/>
     </row>
-    <row r="789" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="789" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B789" s="2"/>
     </row>
-    <row r="790" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="790" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B790" s="2"/>
     </row>
-    <row r="791" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="791" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B791" s="2"/>
     </row>
-    <row r="792" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="792" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B792" s="2"/>
     </row>
-    <row r="793" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="793" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B793" s="2"/>
     </row>
-    <row r="794" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="794" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B794" s="2"/>
     </row>
-    <row r="795" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="795" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B795" s="2"/>
     </row>
-    <row r="796" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="796" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B796" s="2"/>
     </row>
-    <row r="797" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="797" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B797" s="2"/>
     </row>
-    <row r="798" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="798" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B798" s="2"/>
     </row>
-    <row r="799" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="799" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B799" s="2"/>
     </row>
-    <row r="800" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="800" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B800" s="2"/>
     </row>
-    <row r="801" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="801" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B801" s="2"/>
     </row>
-    <row r="802" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="802" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B802" s="2"/>
     </row>
-    <row r="803" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="803" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B803" s="2"/>
     </row>
-    <row r="804" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="804" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B804" s="2"/>
     </row>
-    <row r="805" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="805" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B805" s="2"/>
     </row>
-    <row r="806" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="806" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B806" s="2"/>
     </row>
-    <row r="807" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B807" s="2"/>
     </row>
-    <row r="808" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="808" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B808" s="2"/>
     </row>
-    <row r="809" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="809" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B809" s="2"/>
     </row>
-    <row r="810" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="810" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B810" s="2"/>
     </row>
-    <row r="811" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="811" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B811" s="2"/>
     </row>
-    <row r="812" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="812" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B812" s="2"/>
     </row>
-    <row r="813" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="813" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B813" s="2"/>
     </row>
-    <row r="814" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="814" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B814" s="2"/>
     </row>
-    <row r="815" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="815" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B815" s="2"/>
     </row>
-    <row r="816" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="816" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B816" s="2"/>
     </row>
-    <row r="817" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="817" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B817" s="2"/>
     </row>
-    <row r="818" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="818" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B818" s="2"/>
     </row>
-    <row r="819" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="819" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B819" s="2"/>
     </row>
-    <row r="820" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="820" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B820" s="2"/>
     </row>
-    <row r="821" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B821" s="2"/>
     </row>
-    <row r="822" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B822" s="2"/>
     </row>
-    <row r="823" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B823" s="2"/>
     </row>
-    <row r="824" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B824" s="2"/>
     </row>
-    <row r="825" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B825" s="2"/>
     </row>
-    <row r="826" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B826" s="2"/>
     </row>
-    <row r="827" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B827" s="2"/>
     </row>
-    <row r="828" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B828" s="2"/>
     </row>
-    <row r="829" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B829" s="2"/>
     </row>
-    <row r="830" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B830" s="2"/>
     </row>
-    <row r="831" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="831" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B831" s="2"/>
     </row>
-    <row r="832" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="832" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B832" s="2"/>
     </row>
-    <row r="833" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="833" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B833" s="2"/>
     </row>
-    <row r="834" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="834" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B834" s="2"/>
     </row>
-    <row r="835" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="835" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B835" s="2"/>
     </row>
-    <row r="836" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="836" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B836" s="2"/>
     </row>
-    <row r="837" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="837" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B837" s="2"/>
     </row>
-    <row r="838" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="838" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B838" s="2"/>
     </row>
-    <row r="839" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="839" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B839" s="2"/>
     </row>
-    <row r="840" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="840" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B840" s="2"/>
     </row>
-    <row r="841" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="841" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B841" s="2"/>
     </row>
-    <row r="842" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="842" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B842" s="2"/>
     </row>
-    <row r="843" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="843" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B843" s="2"/>
     </row>
-    <row r="844" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="844" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B844" s="2"/>
     </row>
-    <row r="845" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="845" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B845" s="2"/>
     </row>
-    <row r="846" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="846" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B846" s="2"/>
     </row>
-    <row r="847" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="847" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B847" s="2"/>
     </row>
-    <row r="848" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B848" s="2"/>
     </row>
-    <row r="849" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="849" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B849" s="2"/>
     </row>
-    <row r="850" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="850" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B850" s="2"/>
     </row>
-    <row r="851" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="851" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B851" s="2"/>
     </row>
-    <row r="852" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="852" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B852" s="2"/>
     </row>
-    <row r="853" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="853" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B853" s="2"/>
     </row>
-    <row r="854" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="854" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B854" s="2"/>
     </row>
-    <row r="855" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="855" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B855" s="2"/>
     </row>
-    <row r="856" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="856" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B856" s="2"/>
     </row>
-    <row r="857" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="857" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B857" s="2"/>
     </row>
-    <row r="858" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="858" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B858" s="2"/>
     </row>
-    <row r="859" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="859" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B859" s="2"/>
     </row>
-    <row r="860" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="860" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B860" s="2"/>
     </row>
-    <row r="861" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="861" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B861" s="2"/>
     </row>
-    <row r="862" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="862" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B862" s="2"/>
     </row>
-    <row r="863" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="863" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B863" s="2"/>
     </row>
-    <row r="864" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="864" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B864" s="2"/>
     </row>
-    <row r="865" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="865" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B865" s="2"/>
     </row>
-    <row r="866" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="866" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B866" s="2"/>
     </row>
-    <row r="867" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="867" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B867" s="2"/>
     </row>
-    <row r="868" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="868" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B868" s="2"/>
     </row>
-    <row r="869" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="869" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B869" s="2"/>
     </row>
-    <row r="870" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="870" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B870" s="2"/>
     </row>
-    <row r="871" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="871" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B871" s="2"/>
     </row>
-    <row r="872" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="872" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B872" s="2"/>
     </row>
-    <row r="873" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="873" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B873" s="2"/>
     </row>
-    <row r="874" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="874" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B874" s="2"/>
     </row>
-    <row r="875" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="875" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B875" s="2"/>
     </row>
-    <row r="876" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="876" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B876" s="2"/>
     </row>
-    <row r="877" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="877" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B877" s="2"/>
     </row>
-    <row r="878" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="878" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B878" s="2"/>
     </row>
-    <row r="879" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="879" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B879" s="2"/>
     </row>
-    <row r="880" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="880" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B880" s="2"/>
     </row>
-    <row r="881" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="881" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B881" s="2"/>
     </row>
-    <row r="882" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="882" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B882" s="2"/>
     </row>
-    <row r="883" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="883" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B883" s="2"/>
     </row>
-    <row r="884" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="884" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B884" s="2"/>
     </row>
-    <row r="885" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="885" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B885" s="2"/>
     </row>
-    <row r="886" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="886" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B886" s="2"/>
     </row>
-    <row r="887" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="887" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B887" s="2"/>
     </row>
-    <row r="888" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="888" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B888" s="2"/>
     </row>
-    <row r="889" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="889" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B889" s="2"/>
     </row>
-    <row r="890" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="890" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B890" s="2"/>
     </row>
-    <row r="891" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="891" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B891" s="2"/>
     </row>
-    <row r="892" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="892" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B892" s="2"/>
     </row>
-    <row r="893" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="893" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B893" s="2"/>
     </row>
-    <row r="894" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="894" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B894" s="2"/>
     </row>
-    <row r="895" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="895" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B895" s="2"/>
     </row>
-    <row r="896" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="896" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B896" s="2"/>
     </row>
-    <row r="897" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="897" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B897" s="2"/>
     </row>
-    <row r="898" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B898" s="2"/>
     </row>
-    <row r="899" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="899" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B899" s="2"/>
     </row>
-    <row r="900" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="900" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B900" s="2"/>
     </row>
-    <row r="901" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="901" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B901" s="2"/>
     </row>
-    <row r="902" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="902" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B902" s="2"/>
     </row>
-    <row r="903" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="903" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B903" s="2"/>
     </row>
-    <row r="904" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="904" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B904" s="2"/>
     </row>
-    <row r="905" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="905" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B905" s="2"/>
     </row>
-    <row r="906" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="906" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B906" s="2"/>
     </row>
-    <row r="907" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="907" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B907" s="2"/>
     </row>
-    <row r="908" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="908" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B908" s="2"/>
     </row>
-    <row r="909" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="909" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B909" s="2"/>
     </row>
-    <row r="910" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="910" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B910" s="2"/>
     </row>
-    <row r="911" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="911" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B911" s="2"/>
     </row>
-    <row r="912" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="912" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B912" s="2"/>
     </row>
-    <row r="913" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="913" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B913" s="2"/>
     </row>
-    <row r="914" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="914" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B914" s="2"/>
     </row>
-    <row r="915" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="915" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B915" s="2"/>
     </row>
-    <row r="916" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="916" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B916" s="2"/>
     </row>
-    <row r="917" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="917" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B917" s="2"/>
     </row>
-    <row r="918" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="918" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B918" s="2"/>
     </row>
-    <row r="919" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="919" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B919" s="2"/>
     </row>
-    <row r="920" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="920" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B920" s="2"/>
     </row>
-    <row r="921" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="921" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B921" s="2"/>
     </row>
-    <row r="922" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="922" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B922" s="2"/>
     </row>
-    <row r="923" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="923" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B923" s="2"/>
     </row>
-    <row r="924" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="924" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B924" s="2"/>
     </row>
-    <row r="925" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="925" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B925" s="2"/>
     </row>
-    <row r="926" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="926" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B926" s="2"/>
     </row>
-    <row r="927" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="927" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B927" s="2"/>
     </row>
-    <row r="928" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="928" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B928" s="2"/>
     </row>
-    <row r="929" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="929" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B929" s="2"/>
     </row>
-    <row r="930" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="930" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B930" s="2"/>
     </row>
-    <row r="931" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="931" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B931" s="2"/>
     </row>
-    <row r="932" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="932" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B932" s="2"/>
     </row>
-    <row r="933" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="933" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B933" s="2"/>
     </row>
-    <row r="934" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="934" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B934" s="2"/>
     </row>
-    <row r="935" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="935" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B935" s="2"/>
     </row>
-    <row r="936" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="936" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B936" s="2"/>
     </row>
-    <row r="937" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="937" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B937" s="2"/>
     </row>
-    <row r="938" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="938" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B938" s="2"/>
     </row>
-    <row r="939" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="939" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B939" s="2"/>
     </row>
-    <row r="940" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="940" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B940" s="2"/>
     </row>
-    <row r="941" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="941" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B941" s="2"/>
     </row>
-    <row r="942" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="942" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B942" s="2"/>
     </row>
-    <row r="943" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="943" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B943" s="2"/>
     </row>
-    <row r="944" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="944" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B944" s="2"/>
     </row>
-    <row r="945" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="945" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B945" s="2"/>
     </row>
-    <row r="946" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="946" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B946" s="2"/>
     </row>
-    <row r="947" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="947" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B947" s="2"/>
     </row>
-    <row r="948" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="948" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B948" s="2"/>
     </row>
-    <row r="949" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="949" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B949" s="2"/>
     </row>
-    <row r="950" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="950" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B950" s="2"/>
     </row>
-    <row r="951" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="951" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B951" s="2"/>
     </row>
-    <row r="952" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="952" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B952" s="2"/>
     </row>
-    <row r="953" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="953" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B953" s="2"/>
     </row>
-    <row r="954" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="954" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B954" s="2"/>
     </row>
-    <row r="955" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="955" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B955" s="2"/>
     </row>
-    <row r="956" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="956" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B956" s="2"/>
     </row>
-    <row r="957" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="957" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B957" s="2"/>
     </row>
-    <row r="958" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="958" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B958" s="2"/>
     </row>
-    <row r="959" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="959" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B959" s="2"/>
     </row>
-    <row r="960" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="960" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B960" s="2"/>
     </row>
-    <row r="961" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="961" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B961" s="2"/>
     </row>
-    <row r="962" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="962" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B962" s="2"/>
     </row>
-    <row r="963" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="963" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B963" s="2"/>
     </row>
-    <row r="964" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="964" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B964" s="2"/>
     </row>
-    <row r="965" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="965" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B965" s="2"/>
     </row>
-    <row r="966" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="966" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B966" s="2"/>
     </row>
-    <row r="967" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="967" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B967" s="2"/>
     </row>
-    <row r="968" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="968" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B968" s="2"/>
     </row>
-    <row r="969" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="969" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B969" s="2"/>
     </row>
-    <row r="970" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="970" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B970" s="2"/>
     </row>
-    <row r="971" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="971" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B971" s="2"/>
     </row>
-    <row r="972" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="972" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B972" s="2"/>
     </row>
-    <row r="973" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="973" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B973" s="2"/>
     </row>
-    <row r="974" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="974" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B974" s="2"/>
     </row>
-    <row r="975" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="975" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B975" s="2"/>
     </row>
-    <row r="976" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="976" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B976" s="2"/>
     </row>
-    <row r="977" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="977" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B977" s="2"/>
     </row>
-    <row r="978" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="978" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B978" s="2"/>
     </row>
-    <row r="979" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="979" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B979" s="2"/>
     </row>
-    <row r="980" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="980" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B980" s="2"/>
     </row>
-    <row r="981" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="981" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B981" s="2"/>
     </row>
-    <row r="982" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="982" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B982" s="2"/>
     </row>
-    <row r="983" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="983" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B983" s="2"/>
     </row>
-    <row r="984" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="984" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B984" s="2"/>
     </row>
-    <row r="985" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="985" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B985" s="2"/>
     </row>
-    <row r="986" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="986" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B986" s="2"/>
     </row>
-    <row r="987" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="987" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B987" s="2"/>
     </row>
-    <row r="988" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="988" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B988" s="2"/>
     </row>
-    <row r="989" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="989" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B989" s="2"/>
     </row>
-    <row r="990" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="990" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B990" s="2"/>
     </row>
-    <row r="991" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="991" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B991" s="2"/>
     </row>
-    <row r="992" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="992" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B992" s="2"/>
     </row>
-    <row r="993" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="993" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B993" s="2"/>
     </row>
-    <row r="994" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="994" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B994" s="2"/>
     </row>
-    <row r="995" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="995" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B995" s="2"/>
     </row>
-    <row r="996" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="996" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B996" s="2"/>
     </row>
-    <row r="997" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="997" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B997" s="2"/>
     </row>
-    <row r="998" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="998" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B998" s="2"/>
     </row>
-    <row r="999" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="999" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B999" s="2"/>
     </row>
-    <row r="1000" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1000" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1000" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z183" xr:uid="{B77FC0E0-AD80-4AE8-A6B7-6191F2A456DA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/european_offshore_wind_capex.xlsx
+++ b/data/european_offshore_wind_capex.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdudz\Documents\WindFarm\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF32D48D-F567-4910-9DA2-3034E6CBBC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF49BDC0-EA11-421C-9819-E8F7F9440A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4FCA4BE-944B-479A-AF27-5DDC1E18E177}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4FCA4BE-944B-479A-AF27-5DDC1E18E177}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4218" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4277" uniqueCount="1104">
   <si>
     <t>wind_farm_name</t>
   </si>
@@ -3105,21 +3105,12 @@
     <t>25,9</t>
   </si>
   <si>
-    <t>41.3</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
     <t>0.8</t>
   </si>
   <si>
     <t>0.5</t>
   </si>
   <si>
-    <t>17.05</t>
-  </si>
-  <si>
     <t>105</t>
   </si>
   <si>
@@ -3129,9 +3120,6 @@
     <t>593</t>
   </si>
   <si>
-    <t>59</t>
-  </si>
-  <si>
     <t>36</t>
   </si>
   <si>
@@ -3141,9 +3129,6 @@
     <t>39</t>
   </si>
   <si>
-    <t>22.6</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
@@ -3156,9 +3141,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>1.2</t>
   </si>
   <si>
@@ -3168,9 +3150,6 @@
     <t>132</t>
   </si>
   <si>
-    <t>285</t>
-  </si>
-  <si>
     <t>247</t>
   </si>
   <si>
@@ -3322,6 +3301,78 @@
   </si>
   <si>
     <t>USD 1.71 billion</t>
+  </si>
+  <si>
+    <t>462</t>
+  </si>
+  <si>
+    <t>696</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>599</t>
+  </si>
+  <si>
+    <t>560</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>2850</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>8.7</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>17.5</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>130</t>
   </si>
 </sst>
 </file>
@@ -3789,7 +3840,7 @@
         <v>845</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -3801,10 +3852,10 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
@@ -3868,7 +3919,9 @@
       <c r="C2" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="D2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>468</v>
+      </c>
       <c r="E2" s="1" t="s">
         <v>22</v>
       </c>
@@ -3879,7 +3932,7 @@
         <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
@@ -3944,7 +3997,9 @@
       <c r="C3" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="D3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>1080</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
@@ -3955,7 +4010,7 @@
         <v>34</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
@@ -4020,7 +4075,9 @@
       <c r="C4" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="D4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>1081</v>
+      </c>
       <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
@@ -4031,7 +4088,7 @@
         <v>41</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
@@ -4096,7 +4153,9 @@
       <c r="C5" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>1082</v>
+      </c>
       <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
@@ -4170,7 +4229,9 @@
       <c r="C6" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>1083</v>
+      </c>
       <c r="E6" s="1" t="s">
         <v>22</v>
       </c>
@@ -4244,7 +4305,9 @@
       <c r="C7" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>1084</v>
+      </c>
       <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
@@ -4318,7 +4381,9 @@
       <c r="C8" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
@@ -4329,7 +4394,7 @@
         <v>60</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
@@ -4394,7 +4459,9 @@
       <c r="C9" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>1085</v>
+      </c>
       <c r="E9" s="1" t="s">
         <v>22</v>
       </c>
@@ -4405,7 +4472,7 @@
         <v>67</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
@@ -4470,7 +4537,9 @@
       <c r="C10" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>1086</v>
+      </c>
       <c r="E10" s="1" t="s">
         <v>22</v>
       </c>
@@ -4481,7 +4550,7 @@
         <v>70</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
@@ -4547,7 +4616,7 @@
         <v>855</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>22</v>
@@ -4559,7 +4628,7 @@
         <v>74</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
@@ -4624,7 +4693,9 @@
       <c r="C12" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>1087</v>
+      </c>
       <c r="E12" s="1" t="s">
         <v>22</v>
       </c>
@@ -4635,7 +4706,7 @@
         <v>77</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
@@ -4700,7 +4771,9 @@
       <c r="C13" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>1088</v>
+      </c>
       <c r="E13" s="1" t="s">
         <v>22</v>
       </c>
@@ -4774,7 +4847,9 @@
       <c r="C14" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>1089</v>
+      </c>
       <c r="E14" s="1" t="s">
         <v>22</v>
       </c>
@@ -4848,7 +4923,9 @@
       <c r="C15" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
@@ -4922,7 +4999,9 @@
       <c r="C16" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="E16" s="1" t="s">
         <v>22</v>
       </c>
@@ -4996,7 +5075,9 @@
       <c r="C17" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>302</v>
+      </c>
       <c r="E17" s="1" t="s">
         <v>22</v>
       </c>
@@ -5070,7 +5151,9 @@
       <c r="C18" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="D18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>1090</v>
+      </c>
       <c r="E18" s="1" t="s">
         <v>22</v>
       </c>
@@ -5144,7 +5227,9 @@
       <c r="C19" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="D19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>1091</v>
+      </c>
       <c r="E19" s="1" t="s">
         <v>22</v>
       </c>
@@ -5218,7 +5303,9 @@
       <c r="C20" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="D20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>1088</v>
+      </c>
       <c r="E20" s="1" t="s">
         <v>22</v>
       </c>
@@ -5292,7 +5379,9 @@
       <c r="C21" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="D21" s="5"/>
+      <c r="D21" s="5" t="s">
+        <v>1023</v>
+      </c>
       <c r="E21" s="5" t="s">
         <v>22</v>
       </c>
@@ -5366,7 +5455,9 @@
       <c r="C22" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="D22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>705</v>
+      </c>
       <c r="E22" s="1" t="s">
         <v>22</v>
       </c>
@@ -5440,7 +5531,9 @@
       <c r="C23" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="D23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="E23" s="1" t="s">
         <v>22</v>
       </c>
@@ -5514,7 +5607,9 @@
       <c r="C24" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="D24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>1017</v>
+      </c>
       <c r="E24" s="1" t="s">
         <v>22</v>
       </c>
@@ -5588,7 +5683,9 @@
       <c r="C25" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="D25" s="1"/>
+      <c r="D25" s="1" t="s">
+        <v>1022</v>
+      </c>
       <c r="E25" s="1" t="s">
         <v>22</v>
       </c>
@@ -5662,7 +5759,9 @@
       <c r="C26" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="D26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="E26" s="1" t="s">
         <v>22</v>
       </c>
@@ -5736,7 +5835,9 @@
       <c r="C27" s="5" t="s">
         <v>871</v>
       </c>
-      <c r="D27" s="5"/>
+      <c r="D27" s="5" t="s">
+        <v>175</v>
+      </c>
       <c r="E27" s="5" t="s">
         <v>22</v>
       </c>
@@ -5761,7 +5862,7 @@
         <v>162</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="O27" s="5" t="s">
         <v>30</v>
@@ -5810,7 +5911,9 @@
       <c r="C28" s="5" t="s">
         <v>871</v>
       </c>
-      <c r="D28" s="5"/>
+      <c r="D28" s="5" t="s">
+        <v>238</v>
+      </c>
       <c r="E28" s="5" t="s">
         <v>22</v>
       </c>
@@ -5832,10 +5935,10 @@
         <v>30</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="O28" s="5" t="s">
         <v>30</v>
@@ -5884,7 +5987,9 @@
       <c r="C29" s="5" t="s">
         <v>872</v>
       </c>
-      <c r="D29" s="5"/>
+      <c r="D29" s="5" t="s">
+        <v>1092</v>
+      </c>
       <c r="E29" s="5" t="s">
         <v>22</v>
       </c>
@@ -5958,7 +6063,9 @@
       <c r="C30" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="D30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>1093</v>
+      </c>
       <c r="E30" s="1" t="s">
         <v>22</v>
       </c>
@@ -6032,7 +6139,9 @@
       <c r="C31" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="D31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="E31" s="1" t="s">
         <v>22</v>
       </c>
@@ -6106,7 +6215,9 @@
       <c r="C32" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="D32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="E32" s="1" t="s">
         <v>22</v>
       </c>
@@ -6180,7 +6291,9 @@
       <c r="C33" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="D33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="E33" s="1" t="s">
         <v>22</v>
       </c>
@@ -6254,7 +6367,9 @@
       <c r="C34" s="5" t="s">
         <v>876</v>
       </c>
-      <c r="D34" s="5"/>
+      <c r="D34" s="5" t="s">
+        <v>1094</v>
+      </c>
       <c r="E34" s="5" t="s">
         <v>22</v>
       </c>
@@ -6279,7 +6394,7 @@
         <v>175</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="O34" s="5" t="s">
         <v>30</v>
@@ -6328,7 +6443,9 @@
       <c r="C35" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="D35" s="1"/>
+      <c r="D35" s="1" t="s">
+        <v>231</v>
+      </c>
       <c r="E35" s="1" t="s">
         <v>22</v>
       </c>
@@ -6402,7 +6519,9 @@
       <c r="C36" s="5" t="s">
         <v>873</v>
       </c>
-      <c r="D36" s="5"/>
+      <c r="D36" s="5" t="s">
+        <v>175</v>
+      </c>
       <c r="E36" s="5" t="s">
         <v>22</v>
       </c>
@@ -6427,7 +6546,7 @@
         <v>206</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="O36" s="5" t="s">
         <v>30</v>
@@ -6476,7 +6595,9 @@
       <c r="C37" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="D37" s="1"/>
+      <c r="D37" s="1" t="s">
+        <v>1095</v>
+      </c>
       <c r="E37" s="1" t="s">
         <v>22</v>
       </c>
@@ -6703,7 +6824,7 @@
         <v>881</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>1018</v>
+        <v>1096</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>22</v>
@@ -6729,7 +6850,7 @@
         <v>157</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="O40" s="5" t="s">
         <v>30</v>
@@ -6778,7 +6899,9 @@
       <c r="C41" s="5" t="s">
         <v>882</v>
       </c>
-      <c r="D41" s="5"/>
+      <c r="D41" s="5" t="s">
+        <v>99</v>
+      </c>
       <c r="E41" s="5" t="s">
         <v>22</v>
       </c>
@@ -6877,7 +7000,7 @@
         <v>233</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="O42" s="5" t="s">
         <v>30</v>
@@ -6951,7 +7074,7 @@
         <v>239</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="O43" s="5" t="s">
         <v>30</v>
@@ -7001,7 +7124,7 @@
         <v>885</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>22</v>
@@ -7027,7 +7150,7 @@
         <v>245</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="O44" s="5" t="s">
         <v>30</v>
@@ -7077,7 +7200,7 @@
         <v>886</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>22</v>
@@ -7229,7 +7352,7 @@
         <v>888</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1020</v>
+        <v>1097</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>22</v>
@@ -7305,7 +7428,7 @@
         <v>924</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>22</v>
@@ -7685,7 +7808,7 @@
         <v>891</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1022</v>
+        <v>198</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>280</v>
@@ -7761,7 +7884,7 @@
         <v>927</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>63</v>
+        <v>529</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>280</v>
@@ -7837,7 +7960,7 @@
         <v>927</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1023</v>
+        <v>1098</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>280</v>
@@ -8141,7 +8264,7 @@
         <v>892</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>280</v>
@@ -8217,7 +8340,7 @@
         <v>931</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>586</v>
+        <v>129</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>280</v>
@@ -8369,7 +8492,7 @@
         <v>932</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>280</v>
@@ -8445,7 +8568,7 @@
         <v>933</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>529</v>
+        <v>80</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>280</v>
@@ -8521,7 +8644,7 @@
         <v>933</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>529</v>
+        <v>80</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>280</v>
@@ -8749,7 +8872,7 @@
         <v>895</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>280</v>
@@ -8825,7 +8948,7 @@
         <v>896</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>110</v>
+        <v>615</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>280</v>
@@ -8901,7 +9024,7 @@
         <v>897</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>280</v>
@@ -8977,7 +9100,7 @@
         <v>898</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>280</v>
@@ -9053,7 +9176,7 @@
         <v>935</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>609</v>
+        <v>1027</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>280</v>
@@ -9129,7 +9252,7 @@
         <v>899</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>1026</v>
+        <v>148</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>280</v>
@@ -9383,7 +9506,7 @@
         <v>86</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="O75" s="5" t="s">
         <v>30</v>
@@ -9509,7 +9632,7 @@
         <v>902</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>280</v>
@@ -9585,7 +9708,7 @@
         <v>903</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>280</v>
@@ -9661,7 +9784,7 @@
         <v>904</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>280</v>
@@ -9737,7 +9860,7 @@
         <v>905</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>280</v>
@@ -9839,7 +9962,7 @@
         <v>110</v>
       </c>
       <c r="N81" s="4" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="O81" s="5" t="s">
         <v>30</v>
@@ -9915,7 +10038,7 @@
         <v>110</v>
       </c>
       <c r="N82" s="4" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="O82" s="5" t="s">
         <v>30</v>
@@ -10064,7 +10187,7 @@
         <v>30</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="N84" s="5" t="s">
         <v>403</v>
@@ -10143,7 +10266,7 @@
         <v>216</v>
       </c>
       <c r="N85" s="4" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="O85" s="5" t="s">
         <v>30</v>
@@ -10193,7 +10316,7 @@
         <v>940</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>1015</v>
+        <v>239</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>408</v>
@@ -10269,7 +10392,7 @@
         <v>907</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>408</v>
@@ -10295,7 +10418,7 @@
         <v>420</v>
       </c>
       <c r="N87" s="4" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="O87" s="5" t="s">
         <v>30</v>
@@ -10345,7 +10468,7 @@
         <v>908</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>408</v>
@@ -10421,7 +10544,7 @@
         <v>909</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>92</v>
+        <v>174</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>408</v>
@@ -10497,7 +10620,7 @@
         <v>910</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>408</v>
@@ -10523,7 +10646,7 @@
         <v>436</v>
       </c>
       <c r="N90" s="4" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="O90" s="5" t="s">
         <v>30</v>
@@ -10573,7 +10696,7 @@
         <v>911</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1031</v>
+        <v>1098</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>408</v>
@@ -10675,7 +10798,7 @@
         <v>446</v>
       </c>
       <c r="N92" s="4" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="O92" s="5" t="s">
         <v>30</v>
@@ -10725,7 +10848,7 @@
         <v>912</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>408</v>
@@ -10751,7 +10874,7 @@
         <v>175</v>
       </c>
       <c r="N93" s="4" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="O93" s="5" t="s">
         <v>30</v>
@@ -10801,7 +10924,7 @@
         <v>913</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>129</v>
+        <v>313</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>408</v>
@@ -10903,7 +11026,7 @@
         <v>456</v>
       </c>
       <c r="N95" s="4" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="O95" s="5" t="s">
         <v>30</v>
@@ -11105,7 +11228,7 @@
         <v>927</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>1033</v>
+        <v>517</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>408</v>
@@ -11181,7 +11304,7 @@
         <v>942</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>408</v>
@@ -11409,7 +11532,7 @@
         <v>927</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>1035</v>
+        <v>489</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>408</v>
@@ -11561,7 +11684,7 @@
         <v>944</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>408</v>
@@ -11587,7 +11710,7 @@
         <v>267</v>
       </c>
       <c r="N104" s="4" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="O104" s="5" t="s">
         <v>30</v>
@@ -11713,7 +11836,7 @@
         <v>920</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E106" s="5" t="s">
         <v>497</v>
@@ -11739,7 +11862,7 @@
         <v>231</v>
       </c>
       <c r="N106" s="4" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="O106" s="5" t="s">
         <v>30</v>
@@ -11789,7 +11912,7 @@
         <v>921</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="E107" s="5" t="s">
         <v>497</v>
@@ -11815,7 +11938,7 @@
         <v>180</v>
       </c>
       <c r="N107" s="4" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="O107" s="5" t="s">
         <v>30</v>
@@ -12017,7 +12140,7 @@
         <v>923</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>514</v>
@@ -12092,7 +12215,9 @@
       <c r="C111" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="D111" s="1"/>
+      <c r="D111" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="E111" s="1" t="s">
         <v>514</v>
       </c>
@@ -12166,7 +12291,9 @@
       <c r="C112" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="D112" s="5"/>
+      <c r="D112" s="5" t="s">
+        <v>577</v>
+      </c>
       <c r="E112" s="5" t="s">
         <v>514</v>
       </c>
@@ -12191,7 +12318,7 @@
         <v>267</v>
       </c>
       <c r="N112" s="4" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="O112" s="5" t="s">
         <v>30</v>
@@ -12262,10 +12389,10 @@
         <v>30</v>
       </c>
       <c r="M113" s="4" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="N113" s="4" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="O113" s="5" t="s">
         <v>30</v>
@@ -12339,7 +12466,7 @@
         <v>80</v>
       </c>
       <c r="N114" s="4" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="O114" s="5" t="s">
         <v>30</v>
@@ -12462,7 +12589,9 @@
       <c r="C116" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="D116" s="1"/>
+      <c r="D116" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E116" s="1" t="s">
         <v>537</v>
       </c>
@@ -12536,7 +12665,9 @@
       <c r="C117" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="D117" s="1"/>
+      <c r="D117" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E117" s="1" t="s">
         <v>537</v>
       </c>
@@ -12610,7 +12741,9 @@
       <c r="C118" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="D118" s="1"/>
+      <c r="D118" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="E118" s="1" t="s">
         <v>537</v>
       </c>
@@ -12684,7 +12817,9 @@
       <c r="C119" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="D119" s="1"/>
+      <c r="D119" s="1" t="s">
+        <v>1099</v>
+      </c>
       <c r="E119" s="1" t="s">
         <v>537</v>
       </c>
@@ -12758,7 +12893,9 @@
       <c r="C120" s="5" t="s">
         <v>955</v>
       </c>
-      <c r="D120" s="5"/>
+      <c r="D120" s="5" t="s">
+        <v>1100</v>
+      </c>
       <c r="E120" s="5" t="s">
         <v>537</v>
       </c>
@@ -12783,7 +12920,7 @@
         <v>148</v>
       </c>
       <c r="N120" s="4" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="O120" s="5" t="s">
         <v>30</v>
@@ -12832,7 +12969,9 @@
       <c r="C121" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="D121" s="1"/>
+      <c r="D121" s="1" t="s">
+        <v>1089</v>
+      </c>
       <c r="E121" s="1" t="s">
         <v>537</v>
       </c>
@@ -12931,7 +13070,7 @@
         <v>92</v>
       </c>
       <c r="N122" s="4" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="O122" s="5" t="s">
         <v>30</v>
@@ -12980,7 +13119,9 @@
       <c r="C123" s="5" t="s">
         <v>958</v>
       </c>
-      <c r="D123" s="5"/>
+      <c r="D123" s="5" t="s">
+        <v>1090</v>
+      </c>
       <c r="E123" s="5" t="s">
         <v>537</v>
       </c>
@@ -13005,7 +13146,7 @@
         <v>564</v>
       </c>
       <c r="N123" s="4" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="O123" s="5" t="s">
         <v>30</v>
@@ -13054,7 +13195,9 @@
       <c r="C124" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="D124" s="1"/>
+      <c r="D124" s="1" t="s">
+        <v>1101</v>
+      </c>
       <c r="E124" s="1" t="s">
         <v>537</v>
       </c>
@@ -13128,7 +13271,9 @@
       <c r="C125" s="5" t="s">
         <v>960</v>
       </c>
-      <c r="D125" s="5"/>
+      <c r="D125" s="5" t="s">
+        <v>156</v>
+      </c>
       <c r="E125" s="5" t="s">
         <v>537</v>
       </c>
@@ -13153,7 +13298,7 @@
         <v>571</v>
       </c>
       <c r="N125" s="4" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="O125" s="5" t="s">
         <v>30</v>
@@ -13227,7 +13372,7 @@
         <v>571</v>
       </c>
       <c r="N126" s="4" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
       <c r="O126" s="5" t="s">
         <v>30</v>
@@ -13301,7 +13446,7 @@
         <v>226</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="O127" s="5" t="s">
         <v>30</v>
@@ -13375,7 +13520,7 @@
         <v>226</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="O128" s="5" t="s">
         <v>30</v>
@@ -13449,7 +13594,7 @@
         <v>226</v>
       </c>
       <c r="N129" s="4" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
       <c r="O129" s="5" t="s">
         <v>30</v>
@@ -13523,7 +13668,7 @@
         <v>226</v>
       </c>
       <c r="N130" s="4" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
       <c r="O130" s="5" t="s">
         <v>30</v>
@@ -13745,7 +13890,7 @@
         <v>586</v>
       </c>
       <c r="N133" s="4" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
       <c r="O133" s="5" t="s">
         <v>30</v>
@@ -13816,7 +13961,7 @@
         <v>30</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="N134" s="4" t="s">
         <v>30</v>
@@ -13890,7 +14035,7 @@
         <v>30</v>
       </c>
       <c r="M135" s="4" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="N135" s="4" t="s">
         <v>30</v>
@@ -13942,7 +14087,9 @@
       <c r="C136" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="D136" s="1"/>
+      <c r="D136" s="1" t="s">
+        <v>1022</v>
+      </c>
       <c r="E136" s="1" t="s">
         <v>591</v>
       </c>
@@ -14016,7 +14163,9 @@
       <c r="C137" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="D137" s="1"/>
+      <c r="D137" s="1" t="s">
+        <v>313</v>
+      </c>
       <c r="E137" s="1" t="s">
         <v>591</v>
       </c>
@@ -14090,7 +14239,9 @@
       <c r="C138" s="1" t="s">
         <v>969</v>
       </c>
-      <c r="D138" s="1"/>
+      <c r="D138" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="E138" s="1" t="s">
         <v>591</v>
       </c>
@@ -14164,7 +14315,9 @@
       <c r="C139" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="D139" s="1"/>
+      <c r="D139" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="E139" s="1" t="s">
         <v>591</v>
       </c>
@@ -14238,7 +14391,9 @@
       <c r="C140" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="D140" s="1"/>
+      <c r="D140" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="E140" s="1" t="s">
         <v>591</v>
       </c>
@@ -14312,7 +14467,9 @@
       <c r="C141" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="D141" s="1"/>
+      <c r="D141" s="1" t="s">
+        <v>1027</v>
+      </c>
       <c r="E141" s="1" t="s">
         <v>591</v>
       </c>
@@ -14386,7 +14543,9 @@
       <c r="C142" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="D142" s="1"/>
+      <c r="D142" s="1" t="s">
+        <v>205</v>
+      </c>
       <c r="E142" s="1" t="s">
         <v>591</v>
       </c>
@@ -14707,7 +14866,7 @@
         <v>325</v>
       </c>
       <c r="N146" s="4" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="O146" s="5" t="s">
         <v>30</v>
@@ -14756,7 +14915,9 @@
       <c r="C147" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="D147" s="1"/>
+      <c r="D147" s="1" t="s">
+        <v>1102</v>
+      </c>
       <c r="E147" s="1" t="s">
         <v>633</v>
       </c>
@@ -14830,7 +14991,9 @@
       <c r="C148" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="D148" s="1"/>
+      <c r="D148" s="1" t="s">
+        <v>1023</v>
+      </c>
       <c r="E148" s="1" t="s">
         <v>633</v>
       </c>
@@ -14904,7 +15067,9 @@
       <c r="C149" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="D149" s="1"/>
+      <c r="D149" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="E149" s="1" t="s">
         <v>633</v>
       </c>
@@ -14978,7 +15143,9 @@
       <c r="C150" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="D150" s="1"/>
+      <c r="D150" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="E150" s="1" t="s">
         <v>633</v>
       </c>
@@ -15743,7 +15910,7 @@
         <v>175</v>
       </c>
       <c r="N160" s="4" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="O160" s="5" t="s">
         <v>30</v>
@@ -16039,7 +16206,7 @@
         <v>420</v>
       </c>
       <c r="N164" s="4" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="O164" s="5" t="s">
         <v>30</v>
@@ -16096,7 +16263,7 @@
         <v>66</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="H165" s="4"/>
       <c r="I165" s="4"/>
@@ -16110,7 +16277,7 @@
         <v>30</v>
       </c>
       <c r="M165" s="4" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="N165" s="4" t="s">
         <v>654</v>
@@ -16236,7 +16403,9 @@
       <c r="C167" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="D167" s="1"/>
+      <c r="D167" s="1" t="s">
+        <v>1103</v>
+      </c>
       <c r="E167" s="1" t="s">
         <v>687</v>
       </c>
@@ -17001,7 +17170,7 @@
         <v>717</v>
       </c>
       <c r="N177" s="4" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="O177" s="5" t="s">
         <v>30</v>
@@ -17371,7 +17540,7 @@
         <v>238</v>
       </c>
       <c r="N182" s="4" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="O182" s="5" t="s">
         <v>30</v>
@@ -17442,7 +17611,7 @@
         <v>30</v>
       </c>
       <c r="M183" s="4" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="N183" s="4" t="s">
         <v>30</v>

--- a/data/european_offshore_wind_capex.xlsx
+++ b/data/european_offshore_wind_capex.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdudz\Documents\WindFarm\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\weron\Pulpit\sem3\ds_workshop\WindFarm\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF49BDC0-EA11-421C-9819-E8F7F9440A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EA2E34-C729-48DF-A163-72C9676E799F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4FCA4BE-944B-479A-AF27-5DDC1E18E177}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{D4FCA4BE-944B-479A-AF27-5DDC1E18E177}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4277" uniqueCount="1104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4269" uniqueCount="1103">
   <si>
     <t>wind_farm_name</t>
   </si>
@@ -3229,9 +3229,6 @@
   </si>
   <si>
     <t>turbine_power_MW</t>
-  </si>
-  <si>
-    <t>Siemens</t>
   </si>
   <si>
     <t>203</t>
@@ -3504,9 +3501,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3544,7 +3541,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3650,7 +3647,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3792,7 +3789,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3801,35 +3798,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B77FC0E0-AD80-4AE8-A6B7-6191F2A456DA}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="9" width="20.28515625" customWidth="1"/>
-    <col min="10" max="10" width="45.28515625" customWidth="1"/>
-    <col min="11" max="11" width="28.42578125" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" customWidth="1"/>
-    <col min="13" max="13" width="22.140625" customWidth="1"/>
-    <col min="14" max="14" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" customWidth="1"/>
+    <col min="6" max="6" width="17.6640625" customWidth="1"/>
+    <col min="7" max="9" width="20.33203125" customWidth="1"/>
+    <col min="10" max="10" width="45.33203125" customWidth="1"/>
+    <col min="11" max="11" width="28.44140625" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" customWidth="1"/>
+    <col min="13" max="13" width="22.109375" customWidth="1"/>
+    <col min="14" max="14" width="27.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="23" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3909,7 +3906,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -3931,9 +3928,7 @@
       <c r="G2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>1056</v>
-      </c>
+      <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
         <v>25</v>
@@ -3987,7 +3982,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -3998,7 +3993,7 @@
         <v>847</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>22</v>
@@ -4009,9 +4004,7 @@
       <c r="G3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>1056</v>
-      </c>
+      <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
         <v>35</v>
@@ -4065,7 +4058,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
@@ -4076,7 +4069,7 @@
         <v>848</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>22</v>
@@ -4087,9 +4080,7 @@
       <c r="G4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>1056</v>
-      </c>
+      <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
         <v>42</v>
@@ -4143,7 +4134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>45</v>
       </c>
@@ -4154,7 +4145,7 @@
         <v>849</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>22</v>
@@ -4219,7 +4210,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>54</v>
       </c>
@@ -4230,7 +4221,7 @@
         <v>850</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>22</v>
@@ -4295,7 +4286,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>56</v>
       </c>
@@ -4306,7 +4297,7 @@
         <v>851</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>22</v>
@@ -4371,7 +4362,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
@@ -4393,9 +4384,7 @@
       <c r="G8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>1056</v>
-      </c>
+      <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
         <v>25</v>
@@ -4449,7 +4438,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
@@ -4460,7 +4449,7 @@
         <v>853</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>22</v>
@@ -4471,9 +4460,7 @@
       <c r="G9" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>1056</v>
-      </c>
+      <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1" t="s">
         <v>42</v>
@@ -4527,7 +4514,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>69</v>
       </c>
@@ -4538,7 +4525,7 @@
         <v>854</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>22</v>
@@ -4549,9 +4536,7 @@
       <c r="G10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>1056</v>
-      </c>
+      <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
         <v>42</v>
@@ -4605,7 +4590,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>73</v>
       </c>
@@ -4616,7 +4601,7 @@
         <v>855</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>22</v>
@@ -4627,9 +4612,7 @@
       <c r="G11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>1056</v>
-      </c>
+      <c r="H11" s="1"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
         <v>42</v>
@@ -4683,7 +4666,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>75</v>
       </c>
@@ -4694,7 +4677,7 @@
         <v>856</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>22</v>
@@ -4705,9 +4688,7 @@
       <c r="G12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>1056</v>
-      </c>
+      <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1" t="s">
         <v>78</v>
@@ -4761,7 +4742,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,7 +4753,7 @@
         <v>857</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>22</v>
@@ -4837,7 +4818,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>88</v>
       </c>
@@ -4848,7 +4829,7 @@
         <v>858</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>22</v>
@@ -4913,7 +4894,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>94</v>
       </c>
@@ -4989,7 +4970,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>101</v>
       </c>
@@ -5065,7 +5046,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>106</v>
       </c>
@@ -5141,7 +5122,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>113</v>
       </c>
@@ -5152,7 +5133,7 @@
         <v>862</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>22</v>
@@ -5217,7 +5198,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>118</v>
       </c>
@@ -5228,7 +5209,7 @@
         <v>863</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>22</v>
@@ -5293,7 +5274,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>125</v>
       </c>
@@ -5304,7 +5285,7 @@
         <v>864</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>22</v>
@@ -5369,7 +5350,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>130</v>
       </c>
@@ -5445,7 +5426,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>134</v>
       </c>
@@ -5521,7 +5502,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>140</v>
       </c>
@@ -5597,7 +5578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>145</v>
       </c>
@@ -5673,7 +5654,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>149</v>
       </c>
@@ -5749,7 +5730,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>154</v>
       </c>
@@ -5825,7 +5806,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>159</v>
       </c>
@@ -5901,7 +5882,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>163</v>
       </c>
@@ -5977,7 +5958,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>166</v>
       </c>
@@ -5988,7 +5969,7 @@
         <v>872</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>22</v>
@@ -6053,7 +6034,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>171</v>
       </c>
@@ -6064,7 +6045,7 @@
         <v>873</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>22</v>
@@ -6129,7 +6110,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>177</v>
       </c>
@@ -6205,7 +6186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>181</v>
       </c>
@@ -6281,7 +6262,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>187</v>
       </c>
@@ -6357,7 +6338,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>192</v>
       </c>
@@ -6368,7 +6349,7 @@
         <v>876</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>22</v>
@@ -6433,7 +6414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>196</v>
       </c>
@@ -6509,7 +6490,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>203</v>
       </c>
@@ -6585,7 +6566,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>207</v>
       </c>
@@ -6596,7 +6577,7 @@
         <v>878</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>22</v>
@@ -6661,7 +6642,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>213</v>
       </c>
@@ -6737,7 +6718,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>218</v>
       </c>
@@ -6813,7 +6794,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>221</v>
       </c>
@@ -6824,7 +6805,7 @@
         <v>881</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>22</v>
@@ -6889,7 +6870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>225</v>
       </c>
@@ -6965,7 +6946,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
         <v>229</v>
       </c>
@@ -7039,7 +7020,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>234</v>
       </c>
@@ -7074,7 +7055,7 @@
         <v>239</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="O43" s="5" t="s">
         <v>30</v>
@@ -7113,7 +7094,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
         <v>240</v>
       </c>
@@ -7189,7 +7170,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:26" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>246</v>
       </c>
@@ -7265,7 +7246,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:26" s="12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:26" s="12" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
         <v>251</v>
       </c>
@@ -7341,7 +7322,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>258</v>
       </c>
@@ -7352,7 +7333,7 @@
         <v>888</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>22</v>
@@ -7417,7 +7398,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>261</v>
       </c>
@@ -7493,7 +7474,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>266</v>
       </c>
@@ -7569,7 +7550,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>273</v>
       </c>
@@ -7645,7 +7626,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>279</v>
       </c>
@@ -7721,7 +7702,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>286</v>
       </c>
@@ -7797,7 +7778,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>292</v>
       </c>
@@ -7873,7 +7854,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>297</v>
       </c>
@@ -7949,7 +7930,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>301</v>
       </c>
@@ -7960,7 +7941,7 @@
         <v>927</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>280</v>
@@ -8025,7 +8006,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>304</v>
       </c>
@@ -8101,7 +8082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>308</v>
       </c>
@@ -8177,7 +8158,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="58" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>311</v>
       </c>
@@ -8253,7 +8234,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>314</v>
       </c>
@@ -8329,7 +8310,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>320</v>
       </c>
@@ -8405,7 +8386,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>327</v>
       </c>
@@ -8481,7 +8462,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>329</v>
       </c>
@@ -8557,7 +8538,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>333</v>
       </c>
@@ -8633,7 +8614,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>337</v>
       </c>
@@ -8709,7 +8690,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>339</v>
       </c>
@@ -8785,7 +8766,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>342</v>
       </c>
@@ -8861,7 +8842,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>345</v>
       </c>
@@ -8937,7 +8918,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>347</v>
       </c>
@@ -9013,7 +8994,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>351</v>
       </c>
@@ -9089,7 +9070,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>354</v>
       </c>
@@ -9165,7 +9146,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="71" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>360</v>
       </c>
@@ -9241,7 +9222,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>363</v>
       </c>
@@ -9317,7 +9298,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="73" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>366</v>
       </c>
@@ -9393,7 +9374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="74" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>369</v>
       </c>
@@ -9469,7 +9450,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="75" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
         <v>371</v>
       </c>
@@ -9545,7 +9526,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>375</v>
       </c>
@@ -9621,7 +9602,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>379</v>
       </c>
@@ -9697,7 +9678,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>383</v>
       </c>
@@ -9773,7 +9754,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>388</v>
       </c>
@@ -9849,7 +9830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>391</v>
       </c>
@@ -9925,7 +9906,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="81" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
         <v>393</v>
       </c>
@@ -10001,7 +9982,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
         <v>395</v>
       </c>
@@ -10077,7 +10058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>398</v>
       </c>
@@ -10153,7 +10134,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
         <v>404</v>
       </c>
@@ -10229,7 +10210,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
         <v>405</v>
       </c>
@@ -10305,7 +10286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>407</v>
       </c>
@@ -10381,7 +10362,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
         <v>416</v>
       </c>
@@ -10457,7 +10438,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>421</v>
       </c>
@@ -10533,7 +10514,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>425</v>
       </c>
@@ -10609,7 +10590,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="90" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
         <v>433</v>
       </c>
@@ -10685,7 +10666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>438</v>
       </c>
@@ -10696,7 +10677,7 @@
         <v>911</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>408</v>
@@ -10761,7 +10742,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
         <v>444</v>
       </c>
@@ -10837,7 +10818,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
         <v>447</v>
       </c>
@@ -10913,7 +10894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>450</v>
       </c>
@@ -10989,7 +10970,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
         <v>454</v>
       </c>
@@ -11065,7 +11046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>457</v>
       </c>
@@ -11141,7 +11122,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>462</v>
       </c>
@@ -11217,7 +11198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>467</v>
       </c>
@@ -11293,7 +11274,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>473</v>
       </c>
@@ -11369,7 +11350,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>479</v>
       </c>
@@ -11445,7 +11426,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>484</v>
       </c>
@@ -11521,7 +11502,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>486</v>
       </c>
@@ -11597,7 +11578,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
         <v>488</v>
       </c>
@@ -11673,7 +11654,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
         <v>491</v>
       </c>
@@ -11710,7 +11691,7 @@
         <v>267</v>
       </c>
       <c r="N104" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="O104" s="5" t="s">
         <v>30</v>
@@ -11749,7 +11730,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>493</v>
       </c>
@@ -11825,7 +11806,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
         <v>496</v>
       </c>
@@ -11862,7 +11843,7 @@
         <v>231</v>
       </c>
       <c r="N106" s="4" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="O106" s="5" t="s">
         <v>30</v>
@@ -11901,7 +11882,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
         <v>501</v>
       </c>
@@ -11938,7 +11919,7 @@
         <v>180</v>
       </c>
       <c r="N107" s="4" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="O107" s="5" t="s">
         <v>30</v>
@@ -11977,7 +11958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>505</v>
       </c>
@@ -12053,7 +12034,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>508</v>
       </c>
@@ -12129,7 +12110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>266</v>
       </c>
@@ -12205,7 +12186,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>516</v>
       </c>
@@ -12281,7 +12262,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="112" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
         <v>523</v>
       </c>
@@ -12318,7 +12299,7 @@
         <v>267</v>
       </c>
       <c r="N112" s="4" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="O112" s="5" t="s">
         <v>30</v>
@@ -12357,7 +12338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="113" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
         <v>526</v>
       </c>
@@ -12392,7 +12373,7 @@
         <v>1033</v>
       </c>
       <c r="N113" s="4" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="O113" s="5" t="s">
         <v>30</v>
@@ -12431,7 +12412,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
         <v>527</v>
       </c>
@@ -12466,7 +12447,7 @@
         <v>80</v>
       </c>
       <c r="N114" s="4" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="O114" s="5" t="s">
         <v>30</v>
@@ -12505,7 +12486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
         <v>532</v>
       </c>
@@ -12579,7 +12560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="116" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>536</v>
       </c>
@@ -12655,7 +12636,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="117" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>542</v>
       </c>
@@ -12731,7 +12712,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="118" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>546</v>
       </c>
@@ -12807,7 +12788,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="119" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>548</v>
       </c>
@@ -12818,7 +12799,7 @@
         <v>954</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>537</v>
@@ -12883,7 +12864,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="120" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="5" t="s">
         <v>553</v>
       </c>
@@ -12894,7 +12875,7 @@
         <v>955</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>537</v>
@@ -12920,7 +12901,7 @@
         <v>148</v>
       </c>
       <c r="N120" s="4" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="O120" s="5" t="s">
         <v>30</v>
@@ -12959,7 +12940,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="121" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>556</v>
       </c>
@@ -12970,7 +12951,7 @@
         <v>956</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>537</v>
@@ -13035,7 +13016,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="122" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
         <v>560</v>
       </c>
@@ -13070,7 +13051,7 @@
         <v>92</v>
       </c>
       <c r="N122" s="4" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="O122" s="5" t="s">
         <v>30</v>
@@ -13109,7 +13090,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="123" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
         <v>561</v>
       </c>
@@ -13120,7 +13101,7 @@
         <v>958</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>537</v>
@@ -13146,7 +13127,7 @@
         <v>564</v>
       </c>
       <c r="N123" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="O123" s="5" t="s">
         <v>30</v>
@@ -13185,7 +13166,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="124" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>565</v>
       </c>
@@ -13196,7 +13177,7 @@
         <v>959</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>537</v>
@@ -13261,7 +13242,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
         <v>568</v>
       </c>
@@ -13298,7 +13279,7 @@
         <v>571</v>
       </c>
       <c r="N125" s="4" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="O125" s="5" t="s">
         <v>30</v>
@@ -13337,7 +13318,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="126" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
         <v>572</v>
       </c>
@@ -13372,7 +13353,7 @@
         <v>571</v>
       </c>
       <c r="N126" s="4" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="O126" s="5" t="s">
         <v>30</v>
@@ -13411,7 +13392,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="127" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
         <v>574</v>
       </c>
@@ -13446,7 +13427,7 @@
         <v>226</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="O127" s="5" t="s">
         <v>30</v>
@@ -13485,7 +13466,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="128" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
         <v>575</v>
       </c>
@@ -13520,7 +13501,7 @@
         <v>226</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="O128" s="5" t="s">
         <v>30</v>
@@ -13559,7 +13540,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="129" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
         <v>576</v>
       </c>
@@ -13594,7 +13575,7 @@
         <v>226</v>
       </c>
       <c r="N129" s="4" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="O129" s="5" t="s">
         <v>30</v>
@@ -13633,7 +13614,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="130" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
         <v>578</v>
       </c>
@@ -13668,7 +13649,7 @@
         <v>226</v>
       </c>
       <c r="N130" s="4" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="O130" s="5" t="s">
         <v>30</v>
@@ -13707,7 +13688,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
         <v>579</v>
       </c>
@@ -13781,7 +13762,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="132" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
         <v>581</v>
       </c>
@@ -13855,7 +13836,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
         <v>583</v>
       </c>
@@ -13890,7 +13871,7 @@
         <v>586</v>
       </c>
       <c r="N133" s="4" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="O133" s="5" t="s">
         <v>30</v>
@@ -13929,7 +13910,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
         <v>587</v>
       </c>
@@ -14003,7 +13984,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
         <v>589</v>
       </c>
@@ -14077,7 +14058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>590</v>
       </c>
@@ -14153,7 +14134,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="137" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>596</v>
       </c>
@@ -14229,7 +14210,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>601</v>
       </c>
@@ -14305,7 +14286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="139" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>605</v>
       </c>
@@ -14381,7 +14362,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="140" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>611</v>
       </c>
@@ -14457,7 +14438,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="141" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>617</v>
       </c>
@@ -14533,7 +14514,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="142" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>621</v>
       </c>
@@ -14609,7 +14590,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="143" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>624</v>
       </c>
@@ -14683,7 +14664,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="144" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
         <v>628</v>
       </c>
@@ -14757,7 +14738,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="145" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
         <v>629</v>
       </c>
@@ -14831,7 +14812,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="146" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
         <v>631</v>
       </c>
@@ -14866,7 +14847,7 @@
         <v>325</v>
       </c>
       <c r="N146" s="4" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="O146" s="5" t="s">
         <v>30</v>
@@ -14905,7 +14886,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>632</v>
       </c>
@@ -14916,7 +14897,7 @@
         <v>978</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>633</v>
@@ -14981,7 +14962,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>637</v>
       </c>
@@ -15057,7 +15038,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="149" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>640</v>
       </c>
@@ -15133,7 +15114,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="150" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>643</v>
       </c>
@@ -15209,7 +15190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="151" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>646</v>
       </c>
@@ -15283,7 +15264,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="152" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>651</v>
       </c>
@@ -15357,7 +15338,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="153" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>655</v>
       </c>
@@ -15431,7 +15412,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>656</v>
       </c>
@@ -15505,7 +15486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="155" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>661</v>
       </c>
@@ -15579,7 +15560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="156" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
         <v>665</v>
       </c>
@@ -15653,7 +15634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="157" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
         <v>667</v>
       </c>
@@ -15727,7 +15708,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="158" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>668</v>
       </c>
@@ -15801,7 +15782,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="159" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
         <v>670</v>
       </c>
@@ -15875,7 +15856,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="160" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
         <v>671</v>
       </c>
@@ -15910,7 +15891,7 @@
         <v>175</v>
       </c>
       <c r="N160" s="4" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="O160" s="5" t="s">
         <v>30</v>
@@ -15949,7 +15930,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="161" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>675</v>
       </c>
@@ -16023,7 +16004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="162" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
         <v>677</v>
       </c>
@@ -16097,7 +16078,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
         <v>680</v>
       </c>
@@ -16171,7 +16152,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
         <v>682</v>
       </c>
@@ -16206,7 +16187,7 @@
         <v>420</v>
       </c>
       <c r="N164" s="4" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="O164" s="5" t="s">
         <v>30</v>
@@ -16245,7 +16226,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="165" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
         <v>684</v>
       </c>
@@ -16319,7 +16300,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="166" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
         <v>685</v>
       </c>
@@ -16393,7 +16374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="167" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>686</v>
       </c>
@@ -16404,7 +16385,7 @@
         <v>997</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>687</v>
@@ -16469,7 +16450,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="168" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>690</v>
       </c>
@@ -16543,7 +16524,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="169" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
         <v>694</v>
       </c>
@@ -16617,7 +16598,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="170" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
         <v>696</v>
       </c>
@@ -16691,7 +16672,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="171" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>697</v>
       </c>
@@ -16765,7 +16746,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="172" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>700</v>
       </c>
@@ -16839,7 +16820,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="173" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
         <v>701</v>
       </c>
@@ -16913,7 +16894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
         <v>703</v>
       </c>
@@ -16987,7 +16968,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="175" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>706</v>
       </c>
@@ -17061,7 +17042,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="176" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>709</v>
       </c>
@@ -17135,7 +17116,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="177" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
         <v>713</v>
       </c>
@@ -17170,7 +17151,7 @@
         <v>717</v>
       </c>
       <c r="N177" s="4" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="O177" s="5" t="s">
         <v>30</v>
@@ -17209,7 +17190,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="5" t="s">
         <v>718</v>
       </c>
@@ -17283,7 +17264,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="179" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>720</v>
       </c>
@@ -17357,7 +17338,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>725</v>
       </c>
@@ -17431,7 +17412,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="181" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>731</v>
       </c>
@@ -17505,7 +17486,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="182" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="5" t="s">
         <v>736</v>
       </c>
@@ -17540,7 +17521,7 @@
         <v>238</v>
       </c>
       <c r="N182" s="4" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="O182" s="5" t="s">
         <v>30</v>
@@ -17579,7 +17560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:26" s="7" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:26" s="7" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="5" t="s">
         <v>738</v>
       </c>
@@ -17653,2455 +17634,2455 @@
         <v>30</v>
       </c>
     </row>
-    <row r="184" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B184" s="2"/>
     </row>
-    <row r="185" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B185" s="2"/>
     </row>
-    <row r="186" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B186" s="2"/>
     </row>
-    <row r="187" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B187" s="2"/>
     </row>
-    <row r="188" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B188" s="2"/>
     </row>
-    <row r="189" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B189" s="2"/>
     </row>
-    <row r="190" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B190" s="2"/>
     </row>
-    <row r="191" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B191" s="2"/>
     </row>
-    <row r="192" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B192" s="2"/>
     </row>
-    <row r="193" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B193" s="2"/>
     </row>
-    <row r="194" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B194" s="2"/>
     </row>
-    <row r="195" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B195" s="2"/>
     </row>
-    <row r="196" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B196" s="2"/>
     </row>
-    <row r="197" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B197" s="2"/>
     </row>
-    <row r="198" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B198" s="2"/>
     </row>
-    <row r="199" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B199" s="2"/>
     </row>
-    <row r="200" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B200" s="2"/>
     </row>
-    <row r="201" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B201" s="2"/>
     </row>
-    <row r="202" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B202" s="2"/>
     </row>
-    <row r="203" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B203" s="2"/>
     </row>
-    <row r="204" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B204" s="2"/>
     </row>
-    <row r="205" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B205" s="2"/>
     </row>
-    <row r="206" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B206" s="2"/>
     </row>
-    <row r="207" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B207" s="2"/>
     </row>
-    <row r="208" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B208" s="2"/>
     </row>
-    <row r="209" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B209" s="2"/>
     </row>
-    <row r="210" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B210" s="2"/>
     </row>
-    <row r="211" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B211" s="2"/>
     </row>
-    <row r="212" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B212" s="2"/>
     </row>
-    <row r="213" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B213" s="2"/>
     </row>
-    <row r="214" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B214" s="2"/>
     </row>
-    <row r="215" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B215" s="2"/>
     </row>
-    <row r="216" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B216" s="2"/>
     </row>
-    <row r="217" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B217" s="2"/>
     </row>
-    <row r="218" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B218" s="2"/>
     </row>
-    <row r="219" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B219" s="2"/>
     </row>
-    <row r="220" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B220" s="2"/>
     </row>
-    <row r="221" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B221" s="2"/>
     </row>
-    <row r="222" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B222" s="2"/>
     </row>
-    <row r="223" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B223" s="2"/>
     </row>
-    <row r="224" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B224" s="2"/>
     </row>
-    <row r="225" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B225" s="2"/>
     </row>
-    <row r="226" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B226" s="2"/>
     </row>
-    <row r="227" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B227" s="2"/>
     </row>
-    <row r="228" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B228" s="2"/>
     </row>
-    <row r="229" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B229" s="2"/>
     </row>
-    <row r="230" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B230" s="2"/>
     </row>
-    <row r="231" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B231" s="2"/>
     </row>
-    <row r="232" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B232" s="2"/>
     </row>
-    <row r="233" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B233" s="2"/>
     </row>
-    <row r="234" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B234" s="2"/>
     </row>
-    <row r="235" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B235" s="2"/>
     </row>
-    <row r="236" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B236" s="2"/>
     </row>
-    <row r="237" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B237" s="2"/>
     </row>
-    <row r="238" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B238" s="2"/>
     </row>
-    <row r="239" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B239" s="2"/>
     </row>
-    <row r="240" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B240" s="2"/>
     </row>
-    <row r="241" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B241" s="2"/>
     </row>
-    <row r="242" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B242" s="2"/>
     </row>
-    <row r="243" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B243" s="2"/>
     </row>
-    <row r="244" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B244" s="2"/>
     </row>
-    <row r="245" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B245" s="2"/>
     </row>
-    <row r="246" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B246" s="2"/>
     </row>
-    <row r="247" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B247" s="2"/>
     </row>
-    <row r="248" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B248" s="2"/>
     </row>
-    <row r="249" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B249" s="2"/>
     </row>
-    <row r="250" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B250" s="2"/>
     </row>
-    <row r="251" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B251" s="2"/>
     </row>
-    <row r="252" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B252" s="2"/>
     </row>
-    <row r="253" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B253" s="2"/>
     </row>
-    <row r="254" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B254" s="2"/>
     </row>
-    <row r="255" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B255" s="2"/>
     </row>
-    <row r="256" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B256" s="2"/>
     </row>
-    <row r="257" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B257" s="2"/>
     </row>
-    <row r="258" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B258" s="2"/>
     </row>
-    <row r="259" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B259" s="2"/>
     </row>
-    <row r="260" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B260" s="2"/>
     </row>
-    <row r="261" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B261" s="2"/>
     </row>
-    <row r="262" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B262" s="2"/>
     </row>
-    <row r="263" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B263" s="2"/>
     </row>
-    <row r="264" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B264" s="2"/>
     </row>
-    <row r="265" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B265" s="2"/>
     </row>
-    <row r="266" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B266" s="2"/>
     </row>
-    <row r="267" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B267" s="2"/>
     </row>
-    <row r="268" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B268" s="2"/>
     </row>
-    <row r="269" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B269" s="2"/>
     </row>
-    <row r="270" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B270" s="2"/>
     </row>
-    <row r="271" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B271" s="2"/>
     </row>
-    <row r="272" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B272" s="2"/>
     </row>
-    <row r="273" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B273" s="2"/>
     </row>
-    <row r="274" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B274" s="2"/>
     </row>
-    <row r="275" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B275" s="2"/>
     </row>
-    <row r="276" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B276" s="2"/>
     </row>
-    <row r="277" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B277" s="2"/>
     </row>
-    <row r="278" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B278" s="2"/>
     </row>
-    <row r="279" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B279" s="2"/>
     </row>
-    <row r="280" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B280" s="2"/>
     </row>
-    <row r="281" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B281" s="2"/>
     </row>
-    <row r="282" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B282" s="2"/>
     </row>
-    <row r="283" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B283" s="2"/>
     </row>
-    <row r="284" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B284" s="2"/>
     </row>
-    <row r="285" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B285" s="2"/>
     </row>
-    <row r="286" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B286" s="2"/>
     </row>
-    <row r="287" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B287" s="2"/>
     </row>
-    <row r="288" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B288" s="2"/>
     </row>
-    <row r="289" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B289" s="2"/>
     </row>
-    <row r="290" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B290" s="2"/>
     </row>
-    <row r="291" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B291" s="2"/>
     </row>
-    <row r="292" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B292" s="2"/>
     </row>
-    <row r="293" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B293" s="2"/>
     </row>
-    <row r="294" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B294" s="2"/>
     </row>
-    <row r="295" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B295" s="2"/>
     </row>
-    <row r="296" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B296" s="2"/>
     </row>
-    <row r="297" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B297" s="2"/>
     </row>
-    <row r="298" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B298" s="2"/>
     </row>
-    <row r="299" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B299" s="2"/>
     </row>
-    <row r="300" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B300" s="2"/>
     </row>
-    <row r="301" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B301" s="2"/>
     </row>
-    <row r="302" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B302" s="2"/>
     </row>
-    <row r="303" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B303" s="2"/>
     </row>
-    <row r="304" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B304" s="2"/>
     </row>
-    <row r="305" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B305" s="2"/>
     </row>
-    <row r="306" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B306" s="2"/>
     </row>
-    <row r="307" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B307" s="2"/>
     </row>
-    <row r="308" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B308" s="2"/>
     </row>
-    <row r="309" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B309" s="2"/>
     </row>
-    <row r="310" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B310" s="2"/>
     </row>
-    <row r="311" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B311" s="2"/>
     </row>
-    <row r="312" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B312" s="2"/>
     </row>
-    <row r="313" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B313" s="2"/>
     </row>
-    <row r="314" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B314" s="2"/>
     </row>
-    <row r="315" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B315" s="2"/>
     </row>
-    <row r="316" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B316" s="2"/>
     </row>
-    <row r="317" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B317" s="2"/>
     </row>
-    <row r="318" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B318" s="2"/>
     </row>
-    <row r="319" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B319" s="2"/>
     </row>
-    <row r="320" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B320" s="2"/>
     </row>
-    <row r="321" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B321" s="2"/>
     </row>
-    <row r="322" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B322" s="2"/>
     </row>
-    <row r="323" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B323" s="2"/>
     </row>
-    <row r="324" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B324" s="2"/>
     </row>
-    <row r="325" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B325" s="2"/>
     </row>
-    <row r="326" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B326" s="2"/>
     </row>
-    <row r="327" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B327" s="2"/>
     </row>
-    <row r="328" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B328" s="2"/>
     </row>
-    <row r="329" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B329" s="2"/>
     </row>
-    <row r="330" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B330" s="2"/>
     </row>
-    <row r="331" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B331" s="2"/>
     </row>
-    <row r="332" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B332" s="2"/>
     </row>
-    <row r="333" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B333" s="2"/>
     </row>
-    <row r="334" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B334" s="2"/>
     </row>
-    <row r="335" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B335" s="2"/>
     </row>
-    <row r="336" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B336" s="2"/>
     </row>
-    <row r="337" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B337" s="2"/>
     </row>
-    <row r="338" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B338" s="2"/>
     </row>
-    <row r="339" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B339" s="2"/>
     </row>
-    <row r="340" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B340" s="2"/>
     </row>
-    <row r="341" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B341" s="2"/>
     </row>
-    <row r="342" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B342" s="2"/>
     </row>
-    <row r="343" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B343" s="2"/>
     </row>
-    <row r="344" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B344" s="2"/>
     </row>
-    <row r="345" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B345" s="2"/>
     </row>
-    <row r="346" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B346" s="2"/>
     </row>
-    <row r="347" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B347" s="2"/>
     </row>
-    <row r="348" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B348" s="2"/>
     </row>
-    <row r="349" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B349" s="2"/>
     </row>
-    <row r="350" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B350" s="2"/>
     </row>
-    <row r="351" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B351" s="2"/>
     </row>
-    <row r="352" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B352" s="2"/>
     </row>
-    <row r="353" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B353" s="2"/>
     </row>
-    <row r="354" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B354" s="2"/>
     </row>
-    <row r="355" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B355" s="2"/>
     </row>
-    <row r="356" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B356" s="2"/>
     </row>
-    <row r="357" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B357" s="2"/>
     </row>
-    <row r="358" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B358" s="2"/>
     </row>
-    <row r="359" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B359" s="2"/>
     </row>
-    <row r="360" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B360" s="2"/>
     </row>
-    <row r="361" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B361" s="2"/>
     </row>
-    <row r="362" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B362" s="2"/>
     </row>
-    <row r="363" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B363" s="2"/>
     </row>
-    <row r="364" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B364" s="2"/>
     </row>
-    <row r="365" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B365" s="2"/>
     </row>
-    <row r="366" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B366" s="2"/>
     </row>
-    <row r="367" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B367" s="2"/>
     </row>
-    <row r="368" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B368" s="2"/>
     </row>
-    <row r="369" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B369" s="2"/>
     </row>
-    <row r="370" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B370" s="2"/>
     </row>
-    <row r="371" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B371" s="2"/>
     </row>
-    <row r="372" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B372" s="2"/>
     </row>
-    <row r="373" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B373" s="2"/>
     </row>
-    <row r="374" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B374" s="2"/>
     </row>
-    <row r="375" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B375" s="2"/>
     </row>
-    <row r="376" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B376" s="2"/>
     </row>
-    <row r="377" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B377" s="2"/>
     </row>
-    <row r="378" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B378" s="2"/>
     </row>
-    <row r="379" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B379" s="2"/>
     </row>
-    <row r="380" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B380" s="2"/>
     </row>
-    <row r="381" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B381" s="2"/>
     </row>
-    <row r="382" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B382" s="2"/>
     </row>
-    <row r="383" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B383" s="2"/>
     </row>
-    <row r="384" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B384" s="2"/>
     </row>
-    <row r="385" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B385" s="2"/>
     </row>
-    <row r="386" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B386" s="2"/>
     </row>
-    <row r="387" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B387" s="2"/>
     </row>
-    <row r="388" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B388" s="2"/>
     </row>
-    <row r="389" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B389" s="2"/>
     </row>
-    <row r="390" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B390" s="2"/>
     </row>
-    <row r="391" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B391" s="2"/>
     </row>
-    <row r="392" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B392" s="2"/>
     </row>
-    <row r="393" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B393" s="2"/>
     </row>
-    <row r="394" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B394" s="2"/>
     </row>
-    <row r="395" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B395" s="2"/>
     </row>
-    <row r="396" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B396" s="2"/>
     </row>
-    <row r="397" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B397" s="2"/>
     </row>
-    <row r="398" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B398" s="2"/>
     </row>
-    <row r="399" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B399" s="2"/>
     </row>
-    <row r="400" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B400" s="2"/>
     </row>
-    <row r="401" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B401" s="2"/>
     </row>
-    <row r="402" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B402" s="2"/>
     </row>
-    <row r="403" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B403" s="2"/>
     </row>
-    <row r="404" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B404" s="2"/>
     </row>
-    <row r="405" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B405" s="2"/>
     </row>
-    <row r="406" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B406" s="2"/>
     </row>
-    <row r="407" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B407" s="2"/>
     </row>
-    <row r="408" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B408" s="2"/>
     </row>
-    <row r="409" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B409" s="2"/>
     </row>
-    <row r="410" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B410" s="2"/>
     </row>
-    <row r="411" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B411" s="2"/>
     </row>
-    <row r="412" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B412" s="2"/>
     </row>
-    <row r="413" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B413" s="2"/>
     </row>
-    <row r="414" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B414" s="2"/>
     </row>
-    <row r="415" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B415" s="2"/>
     </row>
-    <row r="416" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B416" s="2"/>
     </row>
-    <row r="417" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B417" s="2"/>
     </row>
-    <row r="418" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B418" s="2"/>
     </row>
-    <row r="419" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B419" s="2"/>
     </row>
-    <row r="420" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B420" s="2"/>
     </row>
-    <row r="421" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B421" s="2"/>
     </row>
-    <row r="422" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B422" s="2"/>
     </row>
-    <row r="423" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B423" s="2"/>
     </row>
-    <row r="424" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B424" s="2"/>
     </row>
-    <row r="425" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B425" s="2"/>
     </row>
-    <row r="426" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B426" s="2"/>
     </row>
-    <row r="427" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B427" s="2"/>
     </row>
-    <row r="428" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B428" s="2"/>
     </row>
-    <row r="429" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B429" s="2"/>
     </row>
-    <row r="430" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B430" s="2"/>
     </row>
-    <row r="431" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B431" s="2"/>
     </row>
-    <row r="432" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B432" s="2"/>
     </row>
-    <row r="433" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B433" s="2"/>
     </row>
-    <row r="434" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B434" s="2"/>
     </row>
-    <row r="435" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B435" s="2"/>
     </row>
-    <row r="436" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B436" s="2"/>
     </row>
-    <row r="437" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B437" s="2"/>
     </row>
-    <row r="438" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B438" s="2"/>
     </row>
-    <row r="439" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B439" s="2"/>
     </row>
-    <row r="440" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B440" s="2"/>
     </row>
-    <row r="441" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B441" s="2"/>
     </row>
-    <row r="442" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B442" s="2"/>
     </row>
-    <row r="443" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B443" s="2"/>
     </row>
-    <row r="444" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B444" s="2"/>
     </row>
-    <row r="445" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B445" s="2"/>
     </row>
-    <row r="446" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B446" s="2"/>
     </row>
-    <row r="447" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B447" s="2"/>
     </row>
-    <row r="448" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B448" s="2"/>
     </row>
-    <row r="449" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B449" s="2"/>
     </row>
-    <row r="450" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B450" s="2"/>
     </row>
-    <row r="451" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B451" s="2"/>
     </row>
-    <row r="452" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B452" s="2"/>
     </row>
-    <row r="453" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B453" s="2"/>
     </row>
-    <row r="454" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B454" s="2"/>
     </row>
-    <row r="455" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B455" s="2"/>
     </row>
-    <row r="456" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B456" s="2"/>
     </row>
-    <row r="457" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B457" s="2"/>
     </row>
-    <row r="458" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B458" s="2"/>
     </row>
-    <row r="459" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B459" s="2"/>
     </row>
-    <row r="460" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B460" s="2"/>
     </row>
-    <row r="461" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B461" s="2"/>
     </row>
-    <row r="462" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B462" s="2"/>
     </row>
-    <row r="463" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B463" s="2"/>
     </row>
-    <row r="464" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B464" s="2"/>
     </row>
-    <row r="465" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B465" s="2"/>
     </row>
-    <row r="466" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B466" s="2"/>
     </row>
-    <row r="467" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B467" s="2"/>
     </row>
-    <row r="468" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B468" s="2"/>
     </row>
-    <row r="469" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B469" s="2"/>
     </row>
-    <row r="470" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B470" s="2"/>
     </row>
-    <row r="471" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B471" s="2"/>
     </row>
-    <row r="472" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B472" s="2"/>
     </row>
-    <row r="473" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B473" s="2"/>
     </row>
-    <row r="474" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B474" s="2"/>
     </row>
-    <row r="475" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B475" s="2"/>
     </row>
-    <row r="476" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B476" s="2"/>
     </row>
-    <row r="477" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B477" s="2"/>
     </row>
-    <row r="478" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B478" s="2"/>
     </row>
-    <row r="479" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B479" s="2"/>
     </row>
-    <row r="480" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B480" s="2"/>
     </row>
-    <row r="481" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B481" s="2"/>
     </row>
-    <row r="482" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B482" s="2"/>
     </row>
-    <row r="483" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B483" s="2"/>
     </row>
-    <row r="484" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B484" s="2"/>
     </row>
-    <row r="485" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B485" s="2"/>
     </row>
-    <row r="486" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B486" s="2"/>
     </row>
-    <row r="487" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B487" s="2"/>
     </row>
-    <row r="488" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B488" s="2"/>
     </row>
-    <row r="489" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B489" s="2"/>
     </row>
-    <row r="490" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B490" s="2"/>
     </row>
-    <row r="491" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B491" s="2"/>
     </row>
-    <row r="492" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B492" s="2"/>
     </row>
-    <row r="493" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B493" s="2"/>
     </row>
-    <row r="494" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B494" s="2"/>
     </row>
-    <row r="495" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B495" s="2"/>
     </row>
-    <row r="496" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B496" s="2"/>
     </row>
-    <row r="497" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B497" s="2"/>
     </row>
-    <row r="498" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B498" s="2"/>
     </row>
-    <row r="499" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B499" s="2"/>
     </row>
-    <row r="500" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B500" s="2"/>
     </row>
-    <row r="501" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B501" s="2"/>
     </row>
-    <row r="502" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B502" s="2"/>
     </row>
-    <row r="503" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B503" s="2"/>
     </row>
-    <row r="504" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B504" s="2"/>
     </row>
-    <row r="505" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B505" s="2"/>
     </row>
-    <row r="506" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B506" s="2"/>
     </row>
-    <row r="507" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B507" s="2"/>
     </row>
-    <row r="508" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B508" s="2"/>
     </row>
-    <row r="509" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B509" s="2"/>
     </row>
-    <row r="510" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B510" s="2"/>
     </row>
-    <row r="511" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B511" s="2"/>
     </row>
-    <row r="512" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B512" s="2"/>
     </row>
-    <row r="513" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B513" s="2"/>
     </row>
-    <row r="514" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B514" s="2"/>
     </row>
-    <row r="515" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B515" s="2"/>
     </row>
-    <row r="516" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B516" s="2"/>
     </row>
-    <row r="517" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B517" s="2"/>
     </row>
-    <row r="518" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B518" s="2"/>
     </row>
-    <row r="519" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B519" s="2"/>
     </row>
-    <row r="520" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B520" s="2"/>
     </row>
-    <row r="521" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B521" s="2"/>
     </row>
-    <row r="522" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B522" s="2"/>
     </row>
-    <row r="523" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B523" s="2"/>
     </row>
-    <row r="524" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B524" s="2"/>
     </row>
-    <row r="525" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B525" s="2"/>
     </row>
-    <row r="526" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B526" s="2"/>
     </row>
-    <row r="527" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B527" s="2"/>
     </row>
-    <row r="528" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B528" s="2"/>
     </row>
-    <row r="529" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B529" s="2"/>
     </row>
-    <row r="530" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B530" s="2"/>
     </row>
-    <row r="531" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B531" s="2"/>
     </row>
-    <row r="532" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B532" s="2"/>
     </row>
-    <row r="533" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B533" s="2"/>
     </row>
-    <row r="534" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B534" s="2"/>
     </row>
-    <row r="535" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B535" s="2"/>
     </row>
-    <row r="536" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B536" s="2"/>
     </row>
-    <row r="537" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B537" s="2"/>
     </row>
-    <row r="538" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B538" s="2"/>
     </row>
-    <row r="539" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B539" s="2"/>
     </row>
-    <row r="540" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B540" s="2"/>
     </row>
-    <row r="541" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B541" s="2"/>
     </row>
-    <row r="542" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B542" s="2"/>
     </row>
-    <row r="543" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B543" s="2"/>
     </row>
-    <row r="544" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B544" s="2"/>
     </row>
-    <row r="545" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B545" s="2"/>
     </row>
-    <row r="546" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B546" s="2"/>
     </row>
-    <row r="547" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B547" s="2"/>
     </row>
-    <row r="548" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B548" s="2"/>
     </row>
-    <row r="549" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B549" s="2"/>
     </row>
-    <row r="550" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B550" s="2"/>
     </row>
-    <row r="551" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B551" s="2"/>
     </row>
-    <row r="552" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B552" s="2"/>
     </row>
-    <row r="553" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B553" s="2"/>
     </row>
-    <row r="554" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B554" s="2"/>
     </row>
-    <row r="555" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B555" s="2"/>
     </row>
-    <row r="556" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B556" s="2"/>
     </row>
-    <row r="557" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B557" s="2"/>
     </row>
-    <row r="558" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B558" s="2"/>
     </row>
-    <row r="559" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B559" s="2"/>
     </row>
-    <row r="560" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B560" s="2"/>
     </row>
-    <row r="561" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B561" s="2"/>
     </row>
-    <row r="562" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B562" s="2"/>
     </row>
-    <row r="563" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B563" s="2"/>
     </row>
-    <row r="564" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B564" s="2"/>
     </row>
-    <row r="565" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B565" s="2"/>
     </row>
-    <row r="566" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B566" s="2"/>
     </row>
-    <row r="567" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B567" s="2"/>
     </row>
-    <row r="568" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B568" s="2"/>
     </row>
-    <row r="569" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B569" s="2"/>
     </row>
-    <row r="570" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B570" s="2"/>
     </row>
-    <row r="571" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B571" s="2"/>
     </row>
-    <row r="572" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B572" s="2"/>
     </row>
-    <row r="573" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B573" s="2"/>
     </row>
-    <row r="574" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B574" s="2"/>
     </row>
-    <row r="575" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B575" s="2"/>
     </row>
-    <row r="576" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B576" s="2"/>
     </row>
-    <row r="577" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B577" s="2"/>
     </row>
-    <row r="578" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B578" s="2"/>
     </row>
-    <row r="579" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B579" s="2"/>
     </row>
-    <row r="580" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B580" s="2"/>
     </row>
-    <row r="581" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B581" s="2"/>
     </row>
-    <row r="582" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B582" s="2"/>
     </row>
-    <row r="583" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B583" s="2"/>
     </row>
-    <row r="584" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B584" s="2"/>
     </row>
-    <row r="585" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B585" s="2"/>
     </row>
-    <row r="586" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B586" s="2"/>
     </row>
-    <row r="587" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B587" s="2"/>
     </row>
-    <row r="588" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B588" s="2"/>
     </row>
-    <row r="589" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B589" s="2"/>
     </row>
-    <row r="590" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B590" s="2"/>
     </row>
-    <row r="591" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B591" s="2"/>
     </row>
-    <row r="592" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B592" s="2"/>
     </row>
-    <row r="593" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B593" s="2"/>
     </row>
-    <row r="594" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B594" s="2"/>
     </row>
-    <row r="595" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B595" s="2"/>
     </row>
-    <row r="596" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B596" s="2"/>
     </row>
-    <row r="597" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B597" s="2"/>
     </row>
-    <row r="598" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B598" s="2"/>
     </row>
-    <row r="599" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B599" s="2"/>
     </row>
-    <row r="600" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B600" s="2"/>
     </row>
-    <row r="601" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B601" s="2"/>
     </row>
-    <row r="602" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B602" s="2"/>
     </row>
-    <row r="603" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B603" s="2"/>
     </row>
-    <row r="604" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B604" s="2"/>
     </row>
-    <row r="605" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B605" s="2"/>
     </row>
-    <row r="606" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B606" s="2"/>
     </row>
-    <row r="607" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B607" s="2"/>
     </row>
-    <row r="608" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B608" s="2"/>
     </row>
-    <row r="609" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B609" s="2"/>
     </row>
-    <row r="610" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B610" s="2"/>
     </row>
-    <row r="611" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B611" s="2"/>
     </row>
-    <row r="612" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B612" s="2"/>
     </row>
-    <row r="613" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B613" s="2"/>
     </row>
-    <row r="614" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B614" s="2"/>
     </row>
-    <row r="615" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B615" s="2"/>
     </row>
-    <row r="616" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B616" s="2"/>
     </row>
-    <row r="617" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B617" s="2"/>
     </row>
-    <row r="618" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B618" s="2"/>
     </row>
-    <row r="619" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B619" s="2"/>
     </row>
-    <row r="620" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B620" s="2"/>
     </row>
-    <row r="621" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B621" s="2"/>
     </row>
-    <row r="622" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B622" s="2"/>
     </row>
-    <row r="623" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B623" s="2"/>
     </row>
-    <row r="624" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B624" s="2"/>
     </row>
-    <row r="625" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B625" s="2"/>
     </row>
-    <row r="626" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B626" s="2"/>
     </row>
-    <row r="627" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B627" s="2"/>
     </row>
-    <row r="628" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B628" s="2"/>
     </row>
-    <row r="629" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B629" s="2"/>
     </row>
-    <row r="630" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B630" s="2"/>
     </row>
-    <row r="631" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B631" s="2"/>
     </row>
-    <row r="632" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B632" s="2"/>
     </row>
-    <row r="633" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B633" s="2"/>
     </row>
-    <row r="634" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B634" s="2"/>
     </row>
-    <row r="635" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B635" s="2"/>
     </row>
-    <row r="636" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B636" s="2"/>
     </row>
-    <row r="637" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B637" s="2"/>
     </row>
-    <row r="638" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B638" s="2"/>
     </row>
-    <row r="639" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B639" s="2"/>
     </row>
-    <row r="640" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B640" s="2"/>
     </row>
-    <row r="641" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B641" s="2"/>
     </row>
-    <row r="642" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B642" s="2"/>
     </row>
-    <row r="643" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B643" s="2"/>
     </row>
-    <row r="644" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B644" s="2"/>
     </row>
-    <row r="645" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B645" s="2"/>
     </row>
-    <row r="646" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B646" s="2"/>
     </row>
-    <row r="647" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B647" s="2"/>
     </row>
-    <row r="648" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B648" s="2"/>
     </row>
-    <row r="649" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B649" s="2"/>
     </row>
-    <row r="650" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B650" s="2"/>
     </row>
-    <row r="651" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B651" s="2"/>
     </row>
-    <row r="652" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B652" s="2"/>
     </row>
-    <row r="653" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B653" s="2"/>
     </row>
-    <row r="654" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B654" s="2"/>
     </row>
-    <row r="655" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B655" s="2"/>
     </row>
-    <row r="656" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B656" s="2"/>
     </row>
-    <row r="657" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B657" s="2"/>
     </row>
-    <row r="658" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B658" s="2"/>
     </row>
-    <row r="659" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B659" s="2"/>
     </row>
-    <row r="660" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B660" s="2"/>
     </row>
-    <row r="661" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B661" s="2"/>
     </row>
-    <row r="662" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B662" s="2"/>
     </row>
-    <row r="663" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B663" s="2"/>
     </row>
-    <row r="664" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B664" s="2"/>
     </row>
-    <row r="665" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B665" s="2"/>
     </row>
-    <row r="666" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B666" s="2"/>
     </row>
-    <row r="667" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B667" s="2"/>
     </row>
-    <row r="668" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B668" s="2"/>
     </row>
-    <row r="669" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B669" s="2"/>
     </row>
-    <row r="670" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B670" s="2"/>
     </row>
-    <row r="671" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B671" s="2"/>
     </row>
-    <row r="672" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B672" s="2"/>
     </row>
-    <row r="673" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B673" s="2"/>
     </row>
-    <row r="674" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B674" s="2"/>
     </row>
-    <row r="675" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B675" s="2"/>
     </row>
-    <row r="676" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B676" s="2"/>
     </row>
-    <row r="677" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B677" s="2"/>
     </row>
-    <row r="678" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B678" s="2"/>
     </row>
-    <row r="679" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B679" s="2"/>
     </row>
-    <row r="680" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B680" s="2"/>
     </row>
-    <row r="681" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B681" s="2"/>
     </row>
-    <row r="682" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B682" s="2"/>
     </row>
-    <row r="683" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B683" s="2"/>
     </row>
-    <row r="684" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B684" s="2"/>
     </row>
-    <row r="685" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B685" s="2"/>
     </row>
-    <row r="686" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B686" s="2"/>
     </row>
-    <row r="687" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B687" s="2"/>
     </row>
-    <row r="688" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B688" s="2"/>
     </row>
-    <row r="689" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B689" s="2"/>
     </row>
-    <row r="690" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B690" s="2"/>
     </row>
-    <row r="691" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B691" s="2"/>
     </row>
-    <row r="692" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B692" s="2"/>
     </row>
-    <row r="693" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B693" s="2"/>
     </row>
-    <row r="694" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B694" s="2"/>
     </row>
-    <row r="695" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B695" s="2"/>
     </row>
-    <row r="696" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B696" s="2"/>
     </row>
-    <row r="697" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B697" s="2"/>
     </row>
-    <row r="698" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B698" s="2"/>
     </row>
-    <row r="699" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B699" s="2"/>
     </row>
-    <row r="700" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B700" s="2"/>
     </row>
-    <row r="701" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B701" s="2"/>
     </row>
-    <row r="702" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B702" s="2"/>
     </row>
-    <row r="703" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B703" s="2"/>
     </row>
-    <row r="704" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B704" s="2"/>
     </row>
-    <row r="705" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B705" s="2"/>
     </row>
-    <row r="706" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B706" s="2"/>
     </row>
-    <row r="707" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B707" s="2"/>
     </row>
-    <row r="708" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B708" s="2"/>
     </row>
-    <row r="709" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B709" s="2"/>
     </row>
-    <row r="710" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B710" s="2"/>
     </row>
-    <row r="711" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B711" s="2"/>
     </row>
-    <row r="712" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B712" s="2"/>
     </row>
-    <row r="713" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B713" s="2"/>
     </row>
-    <row r="714" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B714" s="2"/>
     </row>
-    <row r="715" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B715" s="2"/>
     </row>
-    <row r="716" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B716" s="2"/>
     </row>
-    <row r="717" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B717" s="2"/>
     </row>
-    <row r="718" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B718" s="2"/>
     </row>
-    <row r="719" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B719" s="2"/>
     </row>
-    <row r="720" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B720" s="2"/>
     </row>
-    <row r="721" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B721" s="2"/>
     </row>
-    <row r="722" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B722" s="2"/>
     </row>
-    <row r="723" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B723" s="2"/>
     </row>
-    <row r="724" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B724" s="2"/>
     </row>
-    <row r="725" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B725" s="2"/>
     </row>
-    <row r="726" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B726" s="2"/>
     </row>
-    <row r="727" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B727" s="2"/>
     </row>
-    <row r="728" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B728" s="2"/>
     </row>
-    <row r="729" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B729" s="2"/>
     </row>
-    <row r="730" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B730" s="2"/>
     </row>
-    <row r="731" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B731" s="2"/>
     </row>
-    <row r="732" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B732" s="2"/>
     </row>
-    <row r="733" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B733" s="2"/>
     </row>
-    <row r="734" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B734" s="2"/>
     </row>
-    <row r="735" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B735" s="2"/>
     </row>
-    <row r="736" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B736" s="2"/>
     </row>
-    <row r="737" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B737" s="2"/>
     </row>
-    <row r="738" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B738" s="2"/>
     </row>
-    <row r="739" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B739" s="2"/>
     </row>
-    <row r="740" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B740" s="2"/>
     </row>
-    <row r="741" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B741" s="2"/>
     </row>
-    <row r="742" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B742" s="2"/>
     </row>
-    <row r="743" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B743" s="2"/>
     </row>
-    <row r="744" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B744" s="2"/>
     </row>
-    <row r="745" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B745" s="2"/>
     </row>
-    <row r="746" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B746" s="2"/>
     </row>
-    <row r="747" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B747" s="2"/>
     </row>
-    <row r="748" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B748" s="2"/>
     </row>
-    <row r="749" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B749" s="2"/>
     </row>
-    <row r="750" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B750" s="2"/>
     </row>
-    <row r="751" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B751" s="2"/>
     </row>
-    <row r="752" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B752" s="2"/>
     </row>
-    <row r="753" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B753" s="2"/>
     </row>
-    <row r="754" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B754" s="2"/>
     </row>
-    <row r="755" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B755" s="2"/>
     </row>
-    <row r="756" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B756" s="2"/>
     </row>
-    <row r="757" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B757" s="2"/>
     </row>
-    <row r="758" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B758" s="2"/>
     </row>
-    <row r="759" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B759" s="2"/>
     </row>
-    <row r="760" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B760" s="2"/>
     </row>
-    <row r="761" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B761" s="2"/>
     </row>
-    <row r="762" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B762" s="2"/>
     </row>
-    <row r="763" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B763" s="2"/>
     </row>
-    <row r="764" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B764" s="2"/>
     </row>
-    <row r="765" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B765" s="2"/>
     </row>
-    <row r="766" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B766" s="2"/>
     </row>
-    <row r="767" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B767" s="2"/>
     </row>
-    <row r="768" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B768" s="2"/>
     </row>
-    <row r="769" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B769" s="2"/>
     </row>
-    <row r="770" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B770" s="2"/>
     </row>
-    <row r="771" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B771" s="2"/>
     </row>
-    <row r="772" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B772" s="2"/>
     </row>
-    <row r="773" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B773" s="2"/>
     </row>
-    <row r="774" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B774" s="2"/>
     </row>
-    <row r="775" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B775" s="2"/>
     </row>
-    <row r="776" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B776" s="2"/>
     </row>
-    <row r="777" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B777" s="2"/>
     </row>
-    <row r="778" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B778" s="2"/>
     </row>
-    <row r="779" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B779" s="2"/>
     </row>
-    <row r="780" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B780" s="2"/>
     </row>
-    <row r="781" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B781" s="2"/>
     </row>
-    <row r="782" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B782" s="2"/>
     </row>
-    <row r="783" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B783" s="2"/>
     </row>
-    <row r="784" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B784" s="2"/>
     </row>
-    <row r="785" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B785" s="2"/>
     </row>
-    <row r="786" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B786" s="2"/>
     </row>
-    <row r="787" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B787" s="2"/>
     </row>
-    <row r="788" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B788" s="2"/>
     </row>
-    <row r="789" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="789" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B789" s="2"/>
     </row>
-    <row r="790" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="790" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B790" s="2"/>
     </row>
-    <row r="791" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="791" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B791" s="2"/>
     </row>
-    <row r="792" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="792" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B792" s="2"/>
     </row>
-    <row r="793" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="793" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B793" s="2"/>
     </row>
-    <row r="794" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="794" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B794" s="2"/>
     </row>
-    <row r="795" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B795" s="2"/>
     </row>
-    <row r="796" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="796" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B796" s="2"/>
     </row>
-    <row r="797" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="797" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B797" s="2"/>
     </row>
-    <row r="798" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="798" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B798" s="2"/>
     </row>
-    <row r="799" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="799" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B799" s="2"/>
     </row>
-    <row r="800" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="800" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B800" s="2"/>
     </row>
-    <row r="801" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="801" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B801" s="2"/>
     </row>
-    <row r="802" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="802" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B802" s="2"/>
     </row>
-    <row r="803" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="803" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B803" s="2"/>
     </row>
-    <row r="804" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="804" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B804" s="2"/>
     </row>
-    <row r="805" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="805" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B805" s="2"/>
     </row>
-    <row r="806" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="806" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B806" s="2"/>
     </row>
-    <row r="807" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="807" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B807" s="2"/>
     </row>
-    <row r="808" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="808" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B808" s="2"/>
     </row>
-    <row r="809" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="809" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B809" s="2"/>
     </row>
-    <row r="810" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="810" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B810" s="2"/>
     </row>
-    <row r="811" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="811" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B811" s="2"/>
     </row>
-    <row r="812" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="812" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B812" s="2"/>
     </row>
-    <row r="813" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="813" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B813" s="2"/>
     </row>
-    <row r="814" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="814" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B814" s="2"/>
     </row>
-    <row r="815" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="815" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B815" s="2"/>
     </row>
-    <row r="816" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="816" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B816" s="2"/>
     </row>
-    <row r="817" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="817" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B817" s="2"/>
     </row>
-    <row r="818" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="818" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B818" s="2"/>
     </row>
-    <row r="819" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="819" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B819" s="2"/>
     </row>
-    <row r="820" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="820" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B820" s="2"/>
     </row>
-    <row r="821" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="821" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B821" s="2"/>
     </row>
-    <row r="822" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="822" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B822" s="2"/>
     </row>
-    <row r="823" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="823" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B823" s="2"/>
     </row>
-    <row r="824" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="824" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B824" s="2"/>
     </row>
-    <row r="825" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="825" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B825" s="2"/>
     </row>
-    <row r="826" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="826" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B826" s="2"/>
     </row>
-    <row r="827" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="827" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B827" s="2"/>
     </row>
-    <row r="828" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="828" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B828" s="2"/>
     </row>
-    <row r="829" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B829" s="2"/>
     </row>
-    <row r="830" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="830" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B830" s="2"/>
     </row>
-    <row r="831" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="831" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B831" s="2"/>
     </row>
-    <row r="832" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="832" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B832" s="2"/>
     </row>
-    <row r="833" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="833" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B833" s="2"/>
     </row>
-    <row r="834" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="834" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B834" s="2"/>
     </row>
-    <row r="835" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="835" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B835" s="2"/>
     </row>
-    <row r="836" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="836" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B836" s="2"/>
     </row>
-    <row r="837" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="837" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B837" s="2"/>
     </row>
-    <row r="838" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="838" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B838" s="2"/>
     </row>
-    <row r="839" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="839" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B839" s="2"/>
     </row>
-    <row r="840" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="840" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B840" s="2"/>
     </row>
-    <row r="841" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="841" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B841" s="2"/>
     </row>
-    <row r="842" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="842" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B842" s="2"/>
     </row>
-    <row r="843" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="843" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B843" s="2"/>
     </row>
-    <row r="844" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="844" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B844" s="2"/>
     </row>
-    <row r="845" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="845" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B845" s="2"/>
     </row>
-    <row r="846" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="846" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B846" s="2"/>
     </row>
-    <row r="847" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="847" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B847" s="2"/>
     </row>
-    <row r="848" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="848" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B848" s="2"/>
     </row>
-    <row r="849" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="849" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B849" s="2"/>
     </row>
-    <row r="850" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="850" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B850" s="2"/>
     </row>
-    <row r="851" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="851" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B851" s="2"/>
     </row>
-    <row r="852" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="852" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B852" s="2"/>
     </row>
-    <row r="853" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="853" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B853" s="2"/>
     </row>
-    <row r="854" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="854" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B854" s="2"/>
     </row>
-    <row r="855" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="855" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B855" s="2"/>
     </row>
-    <row r="856" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="856" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B856" s="2"/>
     </row>
-    <row r="857" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="857" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B857" s="2"/>
     </row>
-    <row r="858" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="858" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B858" s="2"/>
     </row>
-    <row r="859" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="859" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B859" s="2"/>
     </row>
-    <row r="860" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="860" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B860" s="2"/>
     </row>
-    <row r="861" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="861" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B861" s="2"/>
     </row>
-    <row r="862" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="862" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B862" s="2"/>
     </row>
-    <row r="863" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="863" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B863" s="2"/>
     </row>
-    <row r="864" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="864" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B864" s="2"/>
     </row>
-    <row r="865" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="865" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B865" s="2"/>
     </row>
-    <row r="866" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="866" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B866" s="2"/>
     </row>
-    <row r="867" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="867" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B867" s="2"/>
     </row>
-    <row r="868" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="868" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B868" s="2"/>
     </row>
-    <row r="869" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="869" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B869" s="2"/>
     </row>
-    <row r="870" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="870" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B870" s="2"/>
     </row>
-    <row r="871" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="871" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B871" s="2"/>
     </row>
-    <row r="872" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="872" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B872" s="2"/>
     </row>
-    <row r="873" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="873" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B873" s="2"/>
     </row>
-    <row r="874" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="874" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B874" s="2"/>
     </row>
-    <row r="875" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="875" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B875" s="2"/>
     </row>
-    <row r="876" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="876" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B876" s="2"/>
     </row>
-    <row r="877" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="877" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B877" s="2"/>
     </row>
-    <row r="878" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="878" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B878" s="2"/>
     </row>
-    <row r="879" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="879" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B879" s="2"/>
     </row>
-    <row r="880" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="880" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B880" s="2"/>
     </row>
-    <row r="881" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="881" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B881" s="2"/>
     </row>
-    <row r="882" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="882" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B882" s="2"/>
     </row>
-    <row r="883" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="883" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B883" s="2"/>
     </row>
-    <row r="884" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="884" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B884" s="2"/>
     </row>
-    <row r="885" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="885" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B885" s="2"/>
     </row>
-    <row r="886" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="886" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B886" s="2"/>
     </row>
-    <row r="887" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="887" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B887" s="2"/>
     </row>
-    <row r="888" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="888" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B888" s="2"/>
     </row>
-    <row r="889" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="889" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B889" s="2"/>
     </row>
-    <row r="890" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="890" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B890" s="2"/>
     </row>
-    <row r="891" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="891" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B891" s="2"/>
     </row>
-    <row r="892" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="892" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B892" s="2"/>
     </row>
-    <row r="893" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="893" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B893" s="2"/>
     </row>
-    <row r="894" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="894" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B894" s="2"/>
     </row>
-    <row r="895" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="895" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B895" s="2"/>
     </row>
-    <row r="896" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="896" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B896" s="2"/>
     </row>
-    <row r="897" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="897" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B897" s="2"/>
     </row>
-    <row r="898" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="898" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B898" s="2"/>
     </row>
-    <row r="899" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="899" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B899" s="2"/>
     </row>
-    <row r="900" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="900" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B900" s="2"/>
     </row>
-    <row r="901" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="901" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B901" s="2"/>
     </row>
-    <row r="902" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="902" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B902" s="2"/>
     </row>
-    <row r="903" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="903" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B903" s="2"/>
     </row>
-    <row r="904" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="904" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B904" s="2"/>
     </row>
-    <row r="905" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="905" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B905" s="2"/>
     </row>
-    <row r="906" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="906" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B906" s="2"/>
     </row>
-    <row r="907" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="907" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B907" s="2"/>
     </row>
-    <row r="908" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="908" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B908" s="2"/>
     </row>
-    <row r="909" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="909" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B909" s="2"/>
     </row>
-    <row r="910" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="910" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B910" s="2"/>
     </row>
-    <row r="911" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="911" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B911" s="2"/>
     </row>
-    <row r="912" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="912" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B912" s="2"/>
     </row>
-    <row r="913" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="913" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B913" s="2"/>
     </row>
-    <row r="914" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="914" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B914" s="2"/>
     </row>
-    <row r="915" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="915" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B915" s="2"/>
     </row>
-    <row r="916" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="916" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B916" s="2"/>
     </row>
-    <row r="917" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="917" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B917" s="2"/>
     </row>
-    <row r="918" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="918" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B918" s="2"/>
     </row>
-    <row r="919" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="919" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B919" s="2"/>
     </row>
-    <row r="920" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="920" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B920" s="2"/>
     </row>
-    <row r="921" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="921" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B921" s="2"/>
     </row>
-    <row r="922" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="922" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B922" s="2"/>
     </row>
-    <row r="923" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="923" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B923" s="2"/>
     </row>
-    <row r="924" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="924" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B924" s="2"/>
     </row>
-    <row r="925" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="925" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B925" s="2"/>
     </row>
-    <row r="926" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="926" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B926" s="2"/>
     </row>
-    <row r="927" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="927" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B927" s="2"/>
     </row>
-    <row r="928" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="928" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B928" s="2"/>
     </row>
-    <row r="929" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="929" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B929" s="2"/>
     </row>
-    <row r="930" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="930" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B930" s="2"/>
     </row>
-    <row r="931" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="931" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B931" s="2"/>
     </row>
-    <row r="932" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="932" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B932" s="2"/>
     </row>
-    <row r="933" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="933" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B933" s="2"/>
     </row>
-    <row r="934" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="934" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B934" s="2"/>
     </row>
-    <row r="935" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="935" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B935" s="2"/>
     </row>
-    <row r="936" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="936" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B936" s="2"/>
     </row>
-    <row r="937" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="937" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B937" s="2"/>
     </row>
-    <row r="938" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="938" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B938" s="2"/>
     </row>
-    <row r="939" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="939" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B939" s="2"/>
     </row>
-    <row r="940" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="940" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B940" s="2"/>
     </row>
-    <row r="941" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="941" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B941" s="2"/>
     </row>
-    <row r="942" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="942" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B942" s="2"/>
     </row>
-    <row r="943" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="943" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B943" s="2"/>
     </row>
-    <row r="944" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="944" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B944" s="2"/>
     </row>
-    <row r="945" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="945" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B945" s="2"/>
     </row>
-    <row r="946" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="946" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B946" s="2"/>
     </row>
-    <row r="947" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="947" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B947" s="2"/>
     </row>
-    <row r="948" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="948" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B948" s="2"/>
     </row>
-    <row r="949" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="949" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B949" s="2"/>
     </row>
-    <row r="950" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="950" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B950" s="2"/>
     </row>
-    <row r="951" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="951" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B951" s="2"/>
     </row>
-    <row r="952" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="952" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B952" s="2"/>
     </row>
-    <row r="953" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="953" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B953" s="2"/>
     </row>
-    <row r="954" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="954" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B954" s="2"/>
     </row>
-    <row r="955" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="955" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B955" s="2"/>
     </row>
-    <row r="956" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="956" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B956" s="2"/>
     </row>
-    <row r="957" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="957" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B957" s="2"/>
     </row>
-    <row r="958" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="958" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B958" s="2"/>
     </row>
-    <row r="959" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="959" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B959" s="2"/>
     </row>
-    <row r="960" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="960" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B960" s="2"/>
     </row>
-    <row r="961" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="961" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B961" s="2"/>
     </row>
-    <row r="962" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="962" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B962" s="2"/>
     </row>
-    <row r="963" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="963" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B963" s="2"/>
     </row>
-    <row r="964" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="964" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B964" s="2"/>
     </row>
-    <row r="965" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="965" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B965" s="2"/>
     </row>
-    <row r="966" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="966" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B966" s="2"/>
     </row>
-    <row r="967" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="967" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B967" s="2"/>
     </row>
-    <row r="968" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="968" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B968" s="2"/>
     </row>
-    <row r="969" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="969" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B969" s="2"/>
     </row>
-    <row r="970" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="970" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B970" s="2"/>
     </row>
-    <row r="971" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="971" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B971" s="2"/>
     </row>
-    <row r="972" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="972" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B972" s="2"/>
     </row>
-    <row r="973" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="973" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B973" s="2"/>
     </row>
-    <row r="974" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="974" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B974" s="2"/>
     </row>
-    <row r="975" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="975" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B975" s="2"/>
     </row>
-    <row r="976" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="976" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B976" s="2"/>
     </row>
-    <row r="977" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="977" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B977" s="2"/>
     </row>
-    <row r="978" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="978" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B978" s="2"/>
     </row>
-    <row r="979" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="979" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B979" s="2"/>
     </row>
-    <row r="980" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="980" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B980" s="2"/>
     </row>
-    <row r="981" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="981" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B981" s="2"/>
     </row>
-    <row r="982" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="982" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B982" s="2"/>
     </row>
-    <row r="983" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="983" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B983" s="2"/>
     </row>
-    <row r="984" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="984" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B984" s="2"/>
     </row>
-    <row r="985" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="985" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B985" s="2"/>
     </row>
-    <row r="986" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="986" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B986" s="2"/>
     </row>
-    <row r="987" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="987" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B987" s="2"/>
     </row>
-    <row r="988" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="988" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B988" s="2"/>
     </row>
-    <row r="989" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="989" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B989" s="2"/>
     </row>
-    <row r="990" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="990" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B990" s="2"/>
     </row>
-    <row r="991" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="991" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B991" s="2"/>
     </row>
-    <row r="992" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="992" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B992" s="2"/>
     </row>
-    <row r="993" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="993" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B993" s="2"/>
     </row>
-    <row r="994" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="994" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B994" s="2"/>
     </row>
-    <row r="995" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="995" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B995" s="2"/>
     </row>
-    <row r="996" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="996" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B996" s="2"/>
     </row>
-    <row r="997" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="997" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B997" s="2"/>
     </row>
-    <row r="998" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="998" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B998" s="2"/>
     </row>
-    <row r="999" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="999" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B999" s="2"/>
     </row>
-    <row r="1000" spans="2:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1000" spans="2:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1000" s="2"/>
     </row>
   </sheetData>
